--- a/gstdatabase/GSTR-3B-2017-2018.xlsx
+++ b/gstdatabase/GSTR-3B-2017-2018.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D35EDA3-D464-4266-A4DE-3C4AD59DEC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DD5A9F-B6DE-475F-9457-4358F1ED7430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -386,7 +386,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -436,6 +436,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -776,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE56"/>
+  <dimension ref="A1:BE58"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
@@ -785,13 +788,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -801,10 +804,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="26"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -831,11 +834,11 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.3">
       <c r="G7" s="11"/>
@@ -848,79 +851,79 @@
       <c r="AP7" s="11"/>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <v>42917</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="22">
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="23">
         <v>42948</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="22">
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="23">
         <v>42979</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="22">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="23">
         <v>43009</v>
       </c>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="22">
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="23">
         <v>43040</v>
       </c>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="22">
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="23">
         <v>43070</v>
       </c>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="23"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="23"/>
-      <c r="AG8" s="22">
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="23">
         <v>43101</v>
       </c>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="23"/>
-      <c r="AJ8" s="23"/>
-      <c r="AK8" s="23"/>
-      <c r="AL8" s="22">
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="24"/>
+      <c r="AL8" s="23">
         <v>43132</v>
       </c>
-      <c r="AM8" s="23"/>
-      <c r="AN8" s="23"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="23"/>
-      <c r="AQ8" s="22">
+      <c r="AM8" s="24"/>
+      <c r="AN8" s="24"/>
+      <c r="AO8" s="24"/>
+      <c r="AP8" s="24"/>
+      <c r="AQ8" s="23">
         <v>43160</v>
       </c>
-      <c r="AR8" s="23"/>
-      <c r="AS8" s="23"/>
-      <c r="AT8" s="23"/>
-      <c r="AU8" s="23"/>
+      <c r="AR8" s="24"/>
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+      <c r="AU8" s="24"/>
     </row>
     <row r="9" spans="1:57" s="7" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="6" t="s">
         <v>3</v>
       </c>
@@ -1189,7 +1192,7 @@
         <f>AE10-AC10</f>
         <v>19782</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AE10" s="22">
         <v>61812</v>
       </c>
       <c r="AF10" s="14">
@@ -1350,7 +1353,7 @@
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
         <v>15735</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AE11" s="22">
         <v>57139</v>
       </c>
       <c r="AF11" s="14">
@@ -1424,14 +1427,14 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="0"/>
-        <v>56532</v>
+        <v>56533</v>
       </c>
       <c r="F12" s="13">
-        <v>213086</v>
+        <v>213087</v>
       </c>
       <c r="G12" s="14">
         <f t="shared" si="1"/>
-        <v>0.96512460029168512</v>
+        <v>0.96512912956437458</v>
       </c>
       <c r="H12" s="12">
         <v>239311</v>
@@ -1441,14 +1444,14 @@
       </c>
       <c r="J12" s="15">
         <f t="shared" si="2"/>
-        <v>85978</v>
+        <v>85979</v>
       </c>
       <c r="K12" s="13">
-        <v>232202</v>
+        <v>232203</v>
       </c>
       <c r="L12" s="14">
         <f t="shared" si="3"/>
-        <v>0.97029388536256167</v>
+        <v>0.97029806402547314</v>
       </c>
       <c r="M12" s="12">
         <v>247374</v>
@@ -1458,14 +1461,14 @@
       </c>
       <c r="O12" s="15">
         <f t="shared" si="4"/>
-        <v>67652</v>
+        <v>67653</v>
       </c>
       <c r="P12" s="13">
-        <v>242986</v>
+        <v>242987</v>
       </c>
       <c r="Q12" s="14">
         <f t="shared" si="5"/>
-        <v>0.98226167665154784</v>
+        <v>0.98226571911356897</v>
       </c>
       <c r="R12" s="12">
         <v>247069</v>
@@ -1475,14 +1478,14 @@
       </c>
       <c r="T12" s="15">
         <f t="shared" si="6"/>
-        <v>56501</v>
+        <v>56502</v>
       </c>
       <c r="U12" s="13">
-        <v>240797</v>
+        <v>240798</v>
       </c>
       <c r="V12" s="14">
         <f t="shared" si="7"/>
-        <v>0.9746143789791516</v>
+        <v>0.97461842643148267</v>
       </c>
       <c r="W12" s="12">
         <v>250968</v>
@@ -1492,14 +1495,14 @@
       </c>
       <c r="Y12" s="15">
         <f t="shared" si="8"/>
-        <v>47585</v>
+        <v>47586</v>
       </c>
       <c r="Z12" s="13">
-        <v>243432</v>
+        <v>243433</v>
       </c>
       <c r="AA12" s="14">
         <f t="shared" si="9"/>
-        <v>0.96997226738070197</v>
+        <v>0.96997625195244019</v>
       </c>
       <c r="AB12" s="12">
         <v>254559</v>
@@ -1509,14 +1512,14 @@
       </c>
       <c r="AD12" s="15">
         <f t="shared" si="10"/>
-        <v>34214</v>
-      </c>
-      <c r="AE12" s="13">
-        <v>245900</v>
+        <v>34215</v>
+      </c>
+      <c r="AE12" s="22">
+        <v>245901</v>
       </c>
       <c r="AF12" s="14">
         <f t="shared" si="11"/>
-        <v>0.96598431012064001</v>
+        <v>0.96598823848302362</v>
       </c>
       <c r="AG12" s="12">
         <v>257888</v>
@@ -1672,7 +1675,7 @@
         <f t="shared" si="10"/>
         <v>4387</v>
       </c>
-      <c r="AE13" s="13">
+      <c r="AE13" s="22">
         <v>23420</v>
       </c>
       <c r="AF13" s="14">
@@ -1763,14 +1766,14 @@
       </c>
       <c r="J14" s="15">
         <f t="shared" si="2"/>
-        <v>62072</v>
+        <v>62073</v>
       </c>
       <c r="K14" s="13">
-        <v>88850</v>
+        <v>88851</v>
       </c>
       <c r="L14" s="14">
         <f t="shared" si="3"/>
-        <v>0.93679160735937583</v>
+        <v>0.93680215087774787</v>
       </c>
       <c r="M14" s="12">
         <v>100078</v>
@@ -1780,14 +1783,14 @@
       </c>
       <c r="O14" s="15">
         <f t="shared" si="4"/>
-        <v>56719</v>
+        <v>56720</v>
       </c>
       <c r="P14" s="13">
-        <v>93505</v>
+        <v>93506</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="5"/>
-        <v>0.93432122944103602</v>
+        <v>0.93433122164711524</v>
       </c>
       <c r="R14" s="12">
         <v>94880</v>
@@ -1814,14 +1817,14 @@
       </c>
       <c r="Y14" s="15">
         <f t="shared" si="8"/>
-        <v>38457</v>
+        <v>38458</v>
       </c>
       <c r="Z14" s="13">
-        <v>89001</v>
+        <v>89002</v>
       </c>
       <c r="AA14" s="14">
         <f t="shared" si="9"/>
-        <v>0.91085957568748654</v>
+        <v>0.91086980994974975</v>
       </c>
       <c r="AB14" s="12">
         <v>99756</v>
@@ -1833,7 +1836,7 @@
         <f t="shared" si="10"/>
         <v>31360</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AE14" s="22">
         <v>90287</v>
       </c>
       <c r="AF14" s="14">
@@ -1848,14 +1851,14 @@
       </c>
       <c r="AI14" s="15">
         <f t="shared" si="12"/>
-        <v>31806</v>
+        <v>31807</v>
       </c>
       <c r="AJ14" s="13">
-        <v>92321</v>
+        <v>92322</v>
       </c>
       <c r="AK14" s="14">
         <f t="shared" si="13"/>
-        <v>0.90018331090699899</v>
+        <v>0.9001930614871585</v>
       </c>
       <c r="AL14" s="12">
         <v>105004</v>
@@ -1941,14 +1944,14 @@
       </c>
       <c r="O15" s="15">
         <f t="shared" si="4"/>
-        <v>125923</v>
+        <v>125924</v>
       </c>
       <c r="P15" s="13">
-        <v>296362</v>
+        <v>296363</v>
       </c>
       <c r="Q15" s="14">
         <f t="shared" si="5"/>
-        <v>0.97861886097141371</v>
+        <v>0.97862216307782735</v>
       </c>
       <c r="R15" s="12">
         <v>306332</v>
@@ -1994,7 +1997,7 @@
         <f t="shared" si="10"/>
         <v>66380</v>
       </c>
-      <c r="AE15" s="13">
+      <c r="AE15" s="22">
         <v>306651</v>
       </c>
       <c r="AF15" s="14">
@@ -2043,14 +2046,14 @@
       </c>
       <c r="AS15" s="15">
         <f t="shared" si="16"/>
-        <v>91729</v>
+        <v>91730</v>
       </c>
       <c r="AT15" s="13">
-        <v>325940</v>
+        <v>325941</v>
       </c>
       <c r="AU15" s="14">
         <f t="shared" si="17"/>
-        <v>0.94754958108273102</v>
+        <v>0.94755248821159244</v>
       </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.3">
@@ -2119,14 +2122,14 @@
       </c>
       <c r="T16" s="15">
         <f t="shared" si="6"/>
-        <v>206758</v>
+        <v>206760</v>
       </c>
       <c r="U16" s="13">
-        <v>519496</v>
+        <v>519498</v>
       </c>
       <c r="V16" s="14">
         <f t="shared" si="7"/>
-        <v>0.97471354083602735</v>
+        <v>0.97471729337133406</v>
       </c>
       <c r="W16" s="12">
         <v>546473</v>
@@ -2155,7 +2158,7 @@
         <f t="shared" si="10"/>
         <v>132877</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AE16" s="22">
         <v>533756</v>
       </c>
       <c r="AF16" s="14">
@@ -2246,14 +2249,14 @@
       </c>
       <c r="J17" s="15">
         <f t="shared" si="2"/>
-        <v>230399</v>
+        <v>230401</v>
       </c>
       <c r="K17" s="13">
-        <v>410474</v>
+        <v>410476</v>
       </c>
       <c r="L17" s="14">
         <f t="shared" si="3"/>
-        <v>0.97051389660594167</v>
+        <v>0.97051862535317834</v>
       </c>
       <c r="M17" s="12">
         <v>435929</v>
@@ -2263,14 +2266,14 @@
       </c>
       <c r="O17" s="15">
         <f t="shared" si="4"/>
-        <v>200003</v>
+        <v>200005</v>
       </c>
       <c r="P17" s="13">
-        <v>425345</v>
+        <v>425347</v>
       </c>
       <c r="Q17" s="14">
         <f t="shared" si="5"/>
-        <v>0.97572081692202173</v>
+        <v>0.97572540482509762</v>
       </c>
       <c r="R17" s="12">
         <v>418736</v>
@@ -2280,14 +2283,14 @@
       </c>
       <c r="T17" s="15">
         <f t="shared" si="6"/>
-        <v>153456</v>
+        <v>153459</v>
       </c>
       <c r="U17" s="13">
-        <v>405788</v>
+        <v>405791</v>
       </c>
       <c r="V17" s="14">
         <f t="shared" si="7"/>
-        <v>0.96907836918726831</v>
+        <v>0.96908553360589966</v>
       </c>
       <c r="W17" s="12">
         <v>427452</v>
@@ -2297,14 +2300,14 @@
       </c>
       <c r="Y17" s="15">
         <f t="shared" si="8"/>
-        <v>127010</v>
+        <v>127012</v>
       </c>
       <c r="Z17" s="13">
-        <v>411158</v>
+        <v>411160</v>
       </c>
       <c r="AA17" s="14">
         <f t="shared" si="9"/>
-        <v>0.96188110010012817</v>
+        <v>0.96188577898805017</v>
       </c>
       <c r="AB17" s="12">
         <v>433360</v>
@@ -2314,14 +2317,14 @@
       </c>
       <c r="AD17" s="15">
         <f t="shared" si="10"/>
-        <v>100707</v>
-      </c>
-      <c r="AE17" s="13">
-        <v>415532</v>
+        <v>100708</v>
+      </c>
+      <c r="AE17" s="22">
+        <v>415533</v>
       </c>
       <c r="AF17" s="14">
         <f t="shared" si="11"/>
-        <v>0.95886099316965112</v>
+        <v>0.95886330071995574</v>
       </c>
       <c r="AG17" s="12">
         <v>442318</v>
@@ -2331,14 +2334,14 @@
       </c>
       <c r="AI17" s="15">
         <f t="shared" si="12"/>
-        <v>112659</v>
+        <v>112660</v>
       </c>
       <c r="AJ17" s="13">
-        <v>422350</v>
+        <v>422351</v>
       </c>
       <c r="AK17" s="14">
         <f t="shared" si="13"/>
-        <v>0.95485600857301756</v>
+        <v>0.95485826938989593</v>
       </c>
       <c r="AL17" s="12">
         <v>449574</v>
@@ -2348,14 +2351,14 @@
       </c>
       <c r="AN17" s="15">
         <f t="shared" si="14"/>
-        <v>117850</v>
+        <v>117851</v>
       </c>
       <c r="AO17" s="13">
-        <v>428785</v>
+        <v>428786</v>
       </c>
       <c r="AP17" s="14">
         <f t="shared" si="15"/>
-        <v>0.95375844688527367</v>
+        <v>0.95376067121319297</v>
       </c>
       <c r="AQ17" s="12">
         <v>455889</v>
@@ -2365,14 +2368,14 @@
       </c>
       <c r="AS17" s="15">
         <f t="shared" si="16"/>
-        <v>143471</v>
+        <v>143472</v>
       </c>
       <c r="AT17" s="13">
-        <v>434563</v>
+        <v>434564</v>
       </c>
       <c r="AU17" s="14">
         <f t="shared" si="17"/>
-        <v>0.9532210691637657</v>
+        <v>0.95322326268016999</v>
       </c>
     </row>
     <row r="18" spans="1:47" x14ac:dyDescent="0.3">
@@ -2424,14 +2427,14 @@
       </c>
       <c r="O18" s="15">
         <f t="shared" si="4"/>
-        <v>403668</v>
+        <v>403669</v>
       </c>
       <c r="P18" s="13">
-        <v>850383</v>
+        <v>850384</v>
       </c>
       <c r="Q18" s="14">
         <f t="shared" si="5"/>
-        <v>0.95779383143212415</v>
+        <v>0.95779495774089496</v>
       </c>
       <c r="R18" s="12">
         <v>809536</v>
@@ -2441,14 +2444,14 @@
       </c>
       <c r="T18" s="15">
         <f t="shared" si="6"/>
-        <v>282964</v>
+        <v>282966</v>
       </c>
       <c r="U18" s="13">
-        <v>769616</v>
+        <v>769618</v>
       </c>
       <c r="V18" s="14">
         <f t="shared" si="7"/>
-        <v>0.95068780140722586</v>
+        <v>0.95069027195825762</v>
       </c>
       <c r="W18" s="12">
         <v>834136</v>
@@ -2458,14 +2461,14 @@
       </c>
       <c r="Y18" s="15">
         <f t="shared" si="8"/>
-        <v>224758</v>
+        <v>224762</v>
       </c>
       <c r="Z18" s="13">
-        <v>784286</v>
+        <v>784290</v>
       </c>
       <c r="AA18" s="14">
         <f t="shared" si="9"/>
-        <v>0.94023756317914586</v>
+        <v>0.94024235856023475</v>
       </c>
       <c r="AB18" s="12">
         <v>847512</v>
@@ -2475,14 +2478,14 @@
       </c>
       <c r="AD18" s="15">
         <f t="shared" si="10"/>
-        <v>171865</v>
-      </c>
-      <c r="AE18" s="13">
-        <v>793319</v>
+        <v>171868</v>
+      </c>
+      <c r="AE18" s="22">
+        <v>793322</v>
       </c>
       <c r="AF18" s="14">
         <f t="shared" si="11"/>
-        <v>0.93605636262377401</v>
+        <v>0.93605990239666226</v>
       </c>
       <c r="AG18" s="12">
         <v>871836</v>
@@ -2492,14 +2495,14 @@
       </c>
       <c r="AI18" s="15">
         <f t="shared" si="12"/>
-        <v>189355</v>
+        <v>189357</v>
       </c>
       <c r="AJ18" s="13">
-        <v>809945</v>
+        <v>809947</v>
       </c>
       <c r="AK18" s="14">
         <f t="shared" si="13"/>
-        <v>0.92901073137608448</v>
+        <v>0.92901302538550823</v>
       </c>
       <c r="AL18" s="12">
         <v>895908</v>
@@ -2509,14 +2512,14 @@
       </c>
       <c r="AN18" s="15">
         <f t="shared" si="14"/>
-        <v>198377</v>
+        <v>198379</v>
       </c>
       <c r="AO18" s="13">
-        <v>829084</v>
+        <v>829086</v>
       </c>
       <c r="AP18" s="14">
         <f t="shared" si="15"/>
-        <v>0.92541198426624161</v>
+        <v>0.92541421663831558</v>
       </c>
       <c r="AQ18" s="12">
         <v>913159</v>
@@ -2526,14 +2529,14 @@
       </c>
       <c r="AS18" s="15">
         <f t="shared" si="16"/>
-        <v>225446</v>
+        <v>225451</v>
       </c>
       <c r="AT18" s="13">
-        <v>845566</v>
+        <v>845571</v>
       </c>
       <c r="AU18" s="14">
         <f t="shared" si="17"/>
-        <v>0.92597893685546551</v>
+        <v>0.92598441235316087</v>
       </c>
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.3">
@@ -2551,14 +2554,14 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="0"/>
-        <v>92038</v>
+        <v>92039</v>
       </c>
       <c r="F19" s="13">
-        <v>175481</v>
+        <v>175482</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="1"/>
-        <v>0.93612333626737088</v>
+        <v>0.93612867088101148</v>
       </c>
       <c r="H19" s="12">
         <v>213585</v>
@@ -2568,14 +2571,14 @@
       </c>
       <c r="J19" s="15">
         <f t="shared" si="2"/>
-        <v>138276</v>
+        <v>138278</v>
       </c>
       <c r="K19" s="13">
-        <v>194285</v>
+        <v>194287</v>
       </c>
       <c r="L19" s="14">
         <f t="shared" si="3"/>
-        <v>0.90963784909988998</v>
+        <v>0.90964721305335117</v>
       </c>
       <c r="M19" s="12">
         <v>222312</v>
@@ -2585,14 +2588,14 @@
       </c>
       <c r="O19" s="15">
         <f t="shared" si="4"/>
-        <v>125347</v>
+        <v>125348</v>
       </c>
       <c r="P19" s="13">
-        <v>204047</v>
+        <v>204048</v>
       </c>
       <c r="Q19" s="14">
         <f t="shared" si="5"/>
-        <v>0.91784069236028643</v>
+        <v>0.91784519054302061</v>
       </c>
       <c r="R19" s="12">
         <v>205062</v>
@@ -2638,7 +2641,7 @@
         <f t="shared" si="10"/>
         <v>73034</v>
       </c>
-      <c r="AE19" s="13">
+      <c r="AE19" s="22">
         <v>195529</v>
       </c>
       <c r="AF19" s="14">
@@ -2799,7 +2802,7 @@
         <f t="shared" si="10"/>
         <v>1440</v>
       </c>
-      <c r="AE20" s="13">
+      <c r="AE20" s="22">
         <v>3761</v>
       </c>
       <c r="AF20" s="14">
@@ -2960,7 +2963,7 @@
         <f t="shared" si="10"/>
         <v>3773</v>
       </c>
-      <c r="AE21" s="13">
+      <c r="AE21" s="22">
         <v>5795</v>
       </c>
       <c r="AF21" s="14">
@@ -3121,7 +3124,7 @@
         <f t="shared" si="10"/>
         <v>2805</v>
       </c>
-      <c r="AE22" s="13">
+      <c r="AE22" s="22">
         <v>4065</v>
       </c>
       <c r="AF22" s="14">
@@ -3282,7 +3285,7 @@
         <f t="shared" si="10"/>
         <v>4109</v>
       </c>
-      <c r="AE23" s="13">
+      <c r="AE23" s="22">
         <v>6210</v>
       </c>
       <c r="AF23" s="14">
@@ -3443,7 +3446,7 @@
         <f t="shared" si="10"/>
         <v>1883</v>
       </c>
-      <c r="AE24" s="13">
+      <c r="AE24" s="22">
         <v>3195</v>
       </c>
       <c r="AF24" s="14">
@@ -3604,7 +3607,7 @@
         <f t="shared" si="10"/>
         <v>6449</v>
       </c>
-      <c r="AE25" s="13">
+      <c r="AE25" s="22">
         <v>15349</v>
       </c>
       <c r="AF25" s="14">
@@ -3765,7 +3768,7 @@
         <f t="shared" si="10"/>
         <v>7131</v>
       </c>
-      <c r="AE26" s="13">
+      <c r="AE26" s="22">
         <v>13383</v>
       </c>
       <c r="AF26" s="14">
@@ -3873,14 +3876,14 @@
       </c>
       <c r="O27" s="15">
         <f t="shared" si="4"/>
-        <v>69268</v>
+        <v>69271</v>
       </c>
       <c r="P27" s="13">
-        <v>99217</v>
+        <v>99220</v>
       </c>
       <c r="Q27" s="14">
         <f t="shared" si="5"/>
-        <v>0.86795671457689982</v>
+        <v>0.86798295877037202</v>
       </c>
       <c r="R27" s="12">
         <v>110497</v>
@@ -3890,14 +3893,14 @@
       </c>
       <c r="T27" s="15">
         <f t="shared" si="6"/>
-        <v>57621</v>
+        <v>57623</v>
       </c>
       <c r="U27" s="13">
-        <v>95404</v>
+        <v>95406</v>
       </c>
       <c r="V27" s="14">
         <f t="shared" si="7"/>
-        <v>0.86340805632732109</v>
+        <v>0.86342615636623621</v>
       </c>
       <c r="W27" s="12">
         <v>113702</v>
@@ -3907,14 +3910,14 @@
       </c>
       <c r="Y27" s="15">
         <f t="shared" si="8"/>
-        <v>53894</v>
+        <v>53895</v>
       </c>
       <c r="Z27" s="13">
-        <v>96864</v>
+        <v>96865</v>
       </c>
       <c r="AA27" s="14">
         <f t="shared" si="9"/>
-        <v>0.85191113612777258</v>
+        <v>0.85191993104782682</v>
       </c>
       <c r="AB27" s="12">
         <v>114563</v>
@@ -3924,14 +3927,14 @@
       </c>
       <c r="AD27" s="15">
         <f t="shared" si="10"/>
-        <v>48864</v>
-      </c>
-      <c r="AE27" s="13">
-        <v>97293</v>
+        <v>48865</v>
+      </c>
+      <c r="AE27" s="22">
+        <v>97294</v>
       </c>
       <c r="AF27" s="14">
         <f t="shared" si="11"/>
-        <v>0.84925324930387647</v>
+        <v>0.8492619781255728</v>
       </c>
       <c r="AG27" s="12">
         <v>116010</v>
@@ -3941,14 +3944,14 @@
       </c>
       <c r="AI27" s="15">
         <f t="shared" si="12"/>
-        <v>47572</v>
+        <v>47573</v>
       </c>
       <c r="AJ27" s="13">
-        <v>98141</v>
+        <v>98142</v>
       </c>
       <c r="AK27" s="14">
         <f t="shared" si="13"/>
-        <v>0.84597017498491511</v>
+        <v>0.84597879493147143</v>
       </c>
       <c r="AL27" s="12">
         <v>119071</v>
@@ -3958,14 +3961,14 @@
       </c>
       <c r="AN27" s="15">
         <f t="shared" si="14"/>
-        <v>49579</v>
+        <v>49580</v>
       </c>
       <c r="AO27" s="13">
-        <v>99834</v>
+        <v>99835</v>
       </c>
       <c r="AP27" s="14">
         <f t="shared" si="15"/>
-        <v>0.8384409302013085</v>
+        <v>0.83844932855187237</v>
       </c>
       <c r="AQ27" s="12">
         <v>122022</v>
@@ -3975,14 +3978,14 @@
       </c>
       <c r="AS27" s="15">
         <f t="shared" si="16"/>
-        <v>57317</v>
+        <v>57318</v>
       </c>
       <c r="AT27" s="13">
-        <v>101983</v>
+        <v>101984</v>
       </c>
       <c r="AU27" s="14">
         <f t="shared" si="17"/>
-        <v>0.83577551589057708</v>
+        <v>0.83578371113405781</v>
       </c>
     </row>
     <row r="28" spans="1:47" x14ac:dyDescent="0.3">
@@ -4000,14 +4003,14 @@
       </c>
       <c r="E28" s="12">
         <f t="shared" si="0"/>
-        <v>106242</v>
+        <v>106243</v>
       </c>
       <c r="F28" s="13">
-        <v>325930</v>
+        <v>325931</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="1"/>
-        <v>0.93922540487579964</v>
+        <v>0.93922828655408908</v>
       </c>
       <c r="H28" s="12">
         <v>405036</v>
@@ -4068,14 +4071,14 @@
       </c>
       <c r="Y28" s="15">
         <f t="shared" si="8"/>
-        <v>140063</v>
+        <v>140064</v>
       </c>
       <c r="Z28" s="13">
-        <v>412810</v>
+        <v>412811</v>
       </c>
       <c r="AA28" s="14">
         <f t="shared" si="9"/>
-        <v>0.9467380984051702</v>
+        <v>0.9467403918043088</v>
       </c>
       <c r="AB28" s="12">
         <v>443892</v>
@@ -4087,7 +4090,7 @@
         <f t="shared" si="10"/>
         <v>124929</v>
       </c>
-      <c r="AE28" s="13">
+      <c r="AE28" s="22">
         <v>419196</v>
       </c>
       <c r="AF28" s="14">
@@ -4195,14 +4198,14 @@
       </c>
       <c r="O29" s="15">
         <f t="shared" si="4"/>
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="P29" s="13">
-        <v>96324</v>
+        <v>96325</v>
       </c>
       <c r="Q29" s="14">
         <f t="shared" si="5"/>
-        <v>0.95668669613149926</v>
+        <v>0.95669662809753186</v>
       </c>
       <c r="R29" s="12">
         <v>101040</v>
@@ -4248,7 +4251,7 @@
         <f t="shared" si="10"/>
         <v>30336</v>
       </c>
-      <c r="AE29" s="13">
+      <c r="AE29" s="22">
         <v>100948</v>
       </c>
       <c r="AF29" s="14">
@@ -4322,14 +4325,14 @@
       </c>
       <c r="E30" s="12">
         <f t="shared" si="0"/>
-        <v>89526</v>
+        <v>89527</v>
       </c>
       <c r="F30" s="13">
-        <v>135035</v>
+        <v>135036</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="1"/>
-        <v>0.96539767649687225</v>
+        <v>0.96540482573726538</v>
       </c>
       <c r="H30" s="12">
         <v>154796</v>
@@ -4339,14 +4342,14 @@
       </c>
       <c r="J30" s="15">
         <f t="shared" si="2"/>
-        <v>101819</v>
+        <v>101820</v>
       </c>
       <c r="K30" s="13">
-        <v>145742</v>
+        <v>145743</v>
       </c>
       <c r="L30" s="14">
         <f t="shared" si="3"/>
-        <v>0.94151011654047911</v>
+        <v>0.94151657665572752</v>
       </c>
       <c r="M30" s="12">
         <v>162133</v>
@@ -4356,14 +4359,14 @@
       </c>
       <c r="O30" s="15">
         <f t="shared" si="4"/>
-        <v>87667</v>
+        <v>87670</v>
       </c>
       <c r="P30" s="13">
-        <v>152005</v>
+        <v>152008</v>
       </c>
       <c r="Q30" s="14">
         <f t="shared" si="5"/>
-        <v>0.93753276630914129</v>
+        <v>0.93755126963665636</v>
       </c>
       <c r="R30" s="12">
         <v>159167</v>
@@ -4373,14 +4376,14 @@
       </c>
       <c r="T30" s="15">
         <f t="shared" si="6"/>
-        <v>71290</v>
+        <v>71292</v>
       </c>
       <c r="U30" s="13">
-        <v>146391</v>
+        <v>146393</v>
       </c>
       <c r="V30" s="14">
         <f t="shared" si="7"/>
-        <v>0.91973210527307792</v>
+        <v>0.91974467069178911</v>
       </c>
       <c r="W30" s="12">
         <v>164732</v>
@@ -4390,14 +4393,14 @@
       </c>
       <c r="Y30" s="15">
         <f t="shared" si="8"/>
-        <v>62452</v>
+        <v>62454</v>
       </c>
       <c r="Z30" s="13">
-        <v>148944</v>
+        <v>148946</v>
       </c>
       <c r="AA30" s="14">
         <f t="shared" si="9"/>
-        <v>0.90415948328193674</v>
+        <v>0.90417162421387465</v>
       </c>
       <c r="AB30" s="12">
         <v>168723</v>
@@ -4407,14 +4410,14 @@
       </c>
       <c r="AD30" s="15">
         <f t="shared" si="10"/>
-        <v>54505</v>
-      </c>
-      <c r="AE30" s="13">
-        <v>151577</v>
+        <v>54506</v>
+      </c>
+      <c r="AE30" s="22">
+        <v>151578</v>
       </c>
       <c r="AF30" s="14">
         <f t="shared" si="11"/>
-        <v>0.89837781452439802</v>
+        <v>0.89838374139862376</v>
       </c>
       <c r="AG30" s="12">
         <v>174193</v>
@@ -4424,14 +4427,14 @@
       </c>
       <c r="AI30" s="15">
         <f t="shared" si="12"/>
-        <v>55406</v>
+        <v>55407</v>
       </c>
       <c r="AJ30" s="13">
-        <v>155539</v>
+        <v>155540</v>
       </c>
       <c r="AK30" s="14">
         <f t="shared" si="13"/>
-        <v>0.89291188509297159</v>
+        <v>0.89291762585178514</v>
       </c>
       <c r="AL30" s="12">
         <v>178748</v>
@@ -4441,14 +4444,14 @@
       </c>
       <c r="AN30" s="15">
         <f t="shared" si="14"/>
-        <v>57516</v>
+        <v>57517</v>
       </c>
       <c r="AO30" s="13">
-        <v>159040</v>
+        <v>159041</v>
       </c>
       <c r="AP30" s="14">
         <f t="shared" si="15"/>
-        <v>0.8897442209143599</v>
+        <v>0.88974981538254971</v>
       </c>
       <c r="AQ30" s="12">
         <v>183516</v>
@@ -4458,14 +4461,14 @@
       </c>
       <c r="AS30" s="15">
         <f t="shared" si="16"/>
-        <v>66218</v>
+        <v>66219</v>
       </c>
       <c r="AT30" s="13">
-        <v>162278</v>
+        <v>162279</v>
       </c>
       <c r="AU30" s="14">
         <f t="shared" si="17"/>
-        <v>0.88427167113494187</v>
+        <v>0.88427712025109528</v>
       </c>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.3">
@@ -4517,14 +4520,14 @@
       </c>
       <c r="O31" s="15">
         <f t="shared" si="4"/>
-        <v>57710</v>
+        <v>57711</v>
       </c>
       <c r="P31" s="13">
-        <v>88375</v>
+        <v>88376</v>
       </c>
       <c r="Q31" s="14">
         <f t="shared" si="5"/>
-        <v>0.9403296340827596</v>
+        <v>0.9403402743049275</v>
       </c>
       <c r="R31" s="12">
         <v>87850</v>
@@ -4534,14 +4537,14 @@
       </c>
       <c r="T31" s="15">
         <f t="shared" si="6"/>
-        <v>47662</v>
+        <v>47663</v>
       </c>
       <c r="U31" s="13">
-        <v>81861</v>
+        <v>81862</v>
       </c>
       <c r="V31" s="14">
         <f t="shared" si="7"/>
-        <v>0.93182697780307344</v>
+        <v>0.93183836084234495</v>
       </c>
       <c r="W31" s="12">
         <v>90015</v>
@@ -4568,14 +4571,14 @@
       </c>
       <c r="AD31" s="15">
         <f t="shared" si="10"/>
-        <v>34622</v>
-      </c>
-      <c r="AE31" s="13">
-        <v>83114</v>
+        <v>34623</v>
+      </c>
+      <c r="AE31" s="22">
+        <v>83115</v>
       </c>
       <c r="AF31" s="14">
         <f t="shared" si="11"/>
-        <v>0.91397341016307998</v>
+        <v>0.91398440678711634</v>
       </c>
       <c r="AG31" s="12">
         <v>92590</v>
@@ -4585,14 +4588,14 @@
       </c>
       <c r="AI31" s="15">
         <f t="shared" si="12"/>
-        <v>34712</v>
+        <v>34713</v>
       </c>
       <c r="AJ31" s="13">
-        <v>84096</v>
+        <v>84097</v>
       </c>
       <c r="AK31" s="14">
         <f t="shared" si="13"/>
-        <v>0.90826223134247763</v>
+        <v>0.90827303164488604</v>
       </c>
       <c r="AL31" s="12">
         <v>93525</v>
@@ -4602,14 +4605,14 @@
       </c>
       <c r="AN31" s="15">
         <f t="shared" si="14"/>
-        <v>35721</v>
+        <v>35722</v>
       </c>
       <c r="AO31" s="13">
-        <v>84916</v>
+        <v>84917</v>
       </c>
       <c r="AP31" s="14">
         <f t="shared" si="15"/>
-        <v>0.90794974605720391</v>
+        <v>0.90796043838545848</v>
       </c>
       <c r="AQ31" s="12">
         <v>94349</v>
@@ -4619,14 +4622,14 @@
       </c>
       <c r="AS31" s="15">
         <f t="shared" si="16"/>
-        <v>42500</v>
+        <v>42501</v>
       </c>
       <c r="AT31" s="13">
-        <v>85508</v>
+        <v>85509</v>
       </c>
       <c r="AU31" s="14">
         <f t="shared" si="17"/>
-        <v>0.9062947143053981</v>
+        <v>0.90630531325186281</v>
       </c>
     </row>
     <row r="32" spans="1:47" x14ac:dyDescent="0.3">
@@ -4678,14 +4681,14 @@
       </c>
       <c r="O32" s="15">
         <f t="shared" si="4"/>
-        <v>166099</v>
+        <v>166100</v>
       </c>
       <c r="P32" s="13">
-        <v>280921</v>
+        <v>280922</v>
       </c>
       <c r="Q32" s="14">
         <f t="shared" si="5"/>
-        <v>0.96752540037885315</v>
+        <v>0.96752884449801968</v>
       </c>
       <c r="R32" s="12">
         <v>274212</v>
@@ -4712,14 +4715,14 @@
       </c>
       <c r="Y32" s="15">
         <f t="shared" si="8"/>
-        <v>101593</v>
+        <v>101594</v>
       </c>
       <c r="Z32" s="13">
-        <v>265433</v>
+        <v>265434</v>
       </c>
       <c r="AA32" s="14">
         <f t="shared" si="9"/>
-        <v>0.94337268895317838</v>
+        <v>0.94337624304286938</v>
       </c>
       <c r="AB32" s="12">
         <v>286853</v>
@@ -4729,14 +4732,14 @@
       </c>
       <c r="AD32" s="15">
         <f t="shared" si="10"/>
-        <v>82133</v>
-      </c>
-      <c r="AE32" s="13">
-        <v>268915</v>
+        <v>82134</v>
+      </c>
+      <c r="AE32" s="22">
+        <v>268916</v>
       </c>
       <c r="AF32" s="14">
         <f t="shared" si="11"/>
-        <v>0.93746622834692339</v>
+        <v>0.93746971445304739</v>
       </c>
       <c r="AG32" s="12">
         <v>294248</v>
@@ -4805,14 +4808,14 @@
       </c>
       <c r="E33" s="12">
         <f t="shared" si="0"/>
-        <v>244049</v>
+        <v>244051</v>
       </c>
       <c r="F33" s="13">
-        <v>555713</v>
+        <v>555715</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="1"/>
-        <v>0.98436600482871861</v>
+        <v>0.98436954754233097</v>
       </c>
       <c r="H33" s="12">
         <v>641658</v>
@@ -4822,14 +4825,14 @@
       </c>
       <c r="J33" s="15">
         <f t="shared" si="2"/>
-        <v>381810</v>
+        <v>381812</v>
       </c>
       <c r="K33" s="13">
-        <v>630526</v>
+        <v>630528</v>
       </c>
       <c r="L33" s="14">
         <f t="shared" si="3"/>
-        <v>0.98265119424989633</v>
+        <v>0.98265431117511193</v>
       </c>
       <c r="M33" s="12">
         <v>682019</v>
@@ -4839,14 +4842,14 @@
       </c>
       <c r="O33" s="15">
         <f t="shared" si="4"/>
-        <v>322821</v>
+        <v>322823</v>
       </c>
       <c r="P33" s="13">
-        <v>671738</v>
+        <v>671740</v>
       </c>
       <c r="Q33" s="14">
         <f t="shared" si="5"/>
-        <v>0.98492563990152771</v>
+        <v>0.98492857237115095</v>
       </c>
       <c r="R33" s="12">
         <v>673475</v>
@@ -4856,14 +4859,14 @@
       </c>
       <c r="T33" s="15">
         <f t="shared" si="6"/>
-        <v>271302</v>
+        <v>271305</v>
       </c>
       <c r="U33" s="13">
-        <v>662047</v>
+        <v>662050</v>
       </c>
       <c r="V33" s="14">
         <f t="shared" si="7"/>
-        <v>0.98303129292104385</v>
+        <v>0.98303574742937749</v>
       </c>
       <c r="W33" s="12">
         <v>688205</v>
@@ -4873,14 +4876,14 @@
       </c>
       <c r="Y33" s="15">
         <f t="shared" si="8"/>
-        <v>206620</v>
+        <v>206622</v>
       </c>
       <c r="Z33" s="13">
-        <v>674444</v>
+        <v>674446</v>
       </c>
       <c r="AA33" s="14">
         <f t="shared" si="9"/>
-        <v>0.980004504471778</v>
+        <v>0.98000741058260255</v>
       </c>
       <c r="AB33" s="12">
         <v>698869</v>
@@ -4892,7 +4895,7 @@
         <f t="shared" si="10"/>
         <v>160026</v>
       </c>
-      <c r="AE33" s="13">
+      <c r="AE33" s="22">
         <v>684446</v>
       </c>
       <c r="AF33" s="14">
@@ -4941,14 +4944,14 @@
       </c>
       <c r="AS33" s="15">
         <f t="shared" si="16"/>
-        <v>199518</v>
+        <v>199520</v>
       </c>
       <c r="AT33" s="13">
-        <v>716002</v>
+        <v>716004</v>
       </c>
       <c r="AU33" s="14">
         <f t="shared" si="17"/>
-        <v>0.97639609933575244</v>
+        <v>0.9763988266915401</v>
       </c>
     </row>
     <row r="34" spans="1:47" x14ac:dyDescent="0.3">
@@ -5053,7 +5056,7 @@
         <f t="shared" si="10"/>
         <v>1611</v>
       </c>
-      <c r="AE34" s="13">
+      <c r="AE34" s="22">
         <v>5049</v>
       </c>
       <c r="AF34" s="14">
@@ -5214,7 +5217,7 @@
         <f t="shared" si="10"/>
         <v>1919</v>
       </c>
-      <c r="AE35" s="13">
+      <c r="AE35" s="22">
         <v>6446</v>
       </c>
       <c r="AF35" s="14">
@@ -5288,14 +5291,14 @@
       </c>
       <c r="E36" s="12">
         <f t="shared" si="0"/>
-        <v>319691</v>
+        <v>319692</v>
       </c>
       <c r="F36" s="13">
-        <v>902373</v>
+        <v>902374</v>
       </c>
       <c r="G36" s="14">
         <f t="shared" si="1"/>
-        <v>0.98631641767552891</v>
+        <v>0.9863175107007166</v>
       </c>
       <c r="H36" s="12">
         <v>1006222</v>
@@ -5305,14 +5308,14 @@
       </c>
       <c r="J36" s="15">
         <f t="shared" si="2"/>
-        <v>566773</v>
+        <v>566774</v>
       </c>
       <c r="K36" s="13">
-        <v>987059</v>
+        <v>987060</v>
       </c>
       <c r="L36" s="14">
         <f t="shared" si="3"/>
-        <v>0.9809554949106658</v>
+        <v>0.9809564887271397</v>
       </c>
       <c r="M36" s="12">
         <v>1060520</v>
@@ -5322,14 +5325,14 @@
       </c>
       <c r="O36" s="15">
         <f t="shared" si="4"/>
-        <v>484931</v>
+        <v>484933</v>
       </c>
       <c r="P36" s="13">
-        <v>1042168</v>
+        <v>1042170</v>
       </c>
       <c r="Q36" s="14">
         <f t="shared" si="5"/>
-        <v>0.98269528155998942</v>
+        <v>0.98269716742729984</v>
       </c>
       <c r="R36" s="12">
         <v>1054857</v>
@@ -5339,14 +5342,14 @@
       </c>
       <c r="T36" s="15">
         <f t="shared" si="6"/>
-        <v>445766</v>
+        <v>445768</v>
       </c>
       <c r="U36" s="13">
-        <v>1031364</v>
+        <v>1031366</v>
       </c>
       <c r="V36" s="14">
         <f t="shared" si="7"/>
-        <v>0.9777287347953324</v>
+        <v>0.97773063078692179</v>
       </c>
       <c r="W36" s="12">
         <v>1076657</v>
@@ -5356,14 +5359,14 @@
       </c>
       <c r="Y36" s="15">
         <f t="shared" si="8"/>
-        <v>379774</v>
+        <v>379775</v>
       </c>
       <c r="Z36" s="13">
-        <v>1046748</v>
+        <v>1046749</v>
       </c>
       <c r="AA36" s="14">
         <f t="shared" si="9"/>
-        <v>0.97222049362053098</v>
+        <v>0.97222142242143972</v>
       </c>
       <c r="AB36" s="12">
         <v>1094504</v>
@@ -5373,14 +5376,14 @@
       </c>
       <c r="AD36" s="15">
         <f t="shared" si="10"/>
-        <v>319158</v>
-      </c>
-      <c r="AE36" s="13">
-        <v>1061365</v>
+        <v>319159</v>
+      </c>
+      <c r="AE36" s="22">
+        <v>1061366</v>
       </c>
       <c r="AF36" s="14">
         <f t="shared" si="11"/>
-        <v>0.96972235825542896</v>
+        <v>0.96972327191129493</v>
       </c>
       <c r="AG36" s="12">
         <v>1114066</v>
@@ -5390,14 +5393,14 @@
       </c>
       <c r="AI36" s="15">
         <f t="shared" si="12"/>
-        <v>353170</v>
+        <v>353172</v>
       </c>
       <c r="AJ36" s="13">
-        <v>1078132</v>
+        <v>1078134</v>
       </c>
       <c r="AK36" s="14">
         <f t="shared" si="13"/>
-        <v>0.96774517847237063</v>
+        <v>0.96774697369814711</v>
       </c>
       <c r="AL36" s="12">
         <v>1133258</v>
@@ -5407,14 +5410,14 @@
       </c>
       <c r="AN36" s="15">
         <f t="shared" si="14"/>
-        <v>353298</v>
+        <v>353301</v>
       </c>
       <c r="AO36" s="13">
-        <v>1095000</v>
+        <v>1095003</v>
       </c>
       <c r="AP36" s="14">
         <f t="shared" si="15"/>
-        <v>0.96624069717575345</v>
+        <v>0.96624334441054027</v>
       </c>
       <c r="AQ36" s="12">
         <v>1148243</v>
@@ -5424,14 +5427,14 @@
       </c>
       <c r="AS36" s="15">
         <f t="shared" si="16"/>
-        <v>377890</v>
+        <v>377892</v>
       </c>
       <c r="AT36" s="13">
-        <v>1108786</v>
+        <v>1108788</v>
       </c>
       <c r="AU36" s="14">
         <f t="shared" si="17"/>
-        <v>0.96563706462830601</v>
+        <v>0.96563880641989541</v>
       </c>
     </row>
     <row r="37" spans="1:47" x14ac:dyDescent="0.3">
@@ -5500,14 +5503,14 @@
       </c>
       <c r="T37" s="15">
         <f t="shared" si="6"/>
-        <v>196447</v>
+        <v>196448</v>
       </c>
       <c r="U37" s="13">
-        <v>514127</v>
+        <v>514128</v>
       </c>
       <c r="V37" s="14">
         <f t="shared" si="7"/>
-        <v>0.9570512975638451</v>
+        <v>0.95705315907140553</v>
       </c>
       <c r="W37" s="12">
         <v>549345</v>
@@ -5534,14 +5537,14 @@
       </c>
       <c r="AD37" s="15">
         <f t="shared" si="10"/>
-        <v>142522</v>
-      </c>
-      <c r="AE37" s="13">
-        <v>523075</v>
+        <v>142525</v>
+      </c>
+      <c r="AE37" s="22">
+        <v>523078</v>
       </c>
       <c r="AF37" s="14">
         <f t="shared" si="11"/>
-        <v>0.94008238469916283</v>
+        <v>0.94008777636795626</v>
       </c>
       <c r="AG37" s="12">
         <v>568190</v>
@@ -5697,7 +5700,7 @@
         <f t="shared" si="10"/>
         <v>9226</v>
       </c>
-      <c r="AE38" s="13">
+      <c r="AE38" s="22">
         <v>24692</v>
       </c>
       <c r="AF38" s="14">
@@ -5858,7 +5861,7 @@
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AE39" s="13">
+      <c r="AE39" s="22">
         <v>167</v>
       </c>
       <c r="AF39" s="14">
@@ -5949,14 +5952,14 @@
       </c>
       <c r="J40" s="15">
         <f t="shared" si="2"/>
-        <v>173194</v>
+        <v>173195</v>
       </c>
       <c r="K40" s="13">
-        <v>225343</v>
+        <v>225344</v>
       </c>
       <c r="L40" s="14">
         <f t="shared" si="3"/>
-        <v>0.99038372793157858</v>
+        <v>0.99038812293709433</v>
       </c>
       <c r="M40" s="12">
         <v>233233</v>
@@ -5966,14 +5969,14 @@
       </c>
       <c r="O40" s="15">
         <f t="shared" si="4"/>
-        <v>114218</v>
+        <v>114219</v>
       </c>
       <c r="P40" s="13">
-        <v>231234</v>
+        <v>231235</v>
       </c>
       <c r="Q40" s="14">
         <f t="shared" si="5"/>
-        <v>0.99142917168668243</v>
+        <v>0.99143345924461801</v>
       </c>
       <c r="R40" s="12">
         <v>227665</v>
@@ -6019,7 +6022,7 @@
         <f t="shared" si="10"/>
         <v>78436</v>
       </c>
-      <c r="AE40" s="13">
+      <c r="AE40" s="22">
         <v>228690</v>
       </c>
       <c r="AF40" s="14">
@@ -6068,14 +6071,14 @@
       </c>
       <c r="AS40" s="15">
         <f t="shared" si="16"/>
-        <v>108294</v>
+        <v>108295</v>
       </c>
       <c r="AT40" s="13">
-        <v>238384</v>
+        <v>238385</v>
       </c>
       <c r="AU40" s="14">
         <f t="shared" si="17"/>
-        <v>0.96998303229560423</v>
+        <v>0.96998710128946419</v>
       </c>
     </row>
     <row r="41" spans="1:47" x14ac:dyDescent="0.3">
@@ -6093,14 +6096,14 @@
       </c>
       <c r="E41" s="12">
         <f t="shared" si="0"/>
-        <v>291276</v>
+        <v>291295</v>
       </c>
       <c r="F41" s="13">
-        <v>603793</v>
+        <v>603812</v>
       </c>
       <c r="G41" s="14">
         <f t="shared" si="1"/>
-        <v>0.96627596956787531</v>
+        <v>0.96630637608703307</v>
       </c>
       <c r="H41" s="12">
         <v>673862</v>
@@ -6110,14 +6113,14 @@
       </c>
       <c r="J41" s="15">
         <f t="shared" si="2"/>
-        <v>440781</v>
+        <v>440797</v>
       </c>
       <c r="K41" s="13">
-        <v>643225</v>
+        <v>643241</v>
       </c>
       <c r="L41" s="14">
         <f t="shared" si="3"/>
-        <v>0.95453520156946081</v>
+        <v>0.95455894530334107</v>
       </c>
       <c r="M41" s="12">
         <v>700632</v>
@@ -6127,14 +6130,14 @@
       </c>
       <c r="O41" s="15">
         <f t="shared" si="4"/>
-        <v>341577</v>
+        <v>341593</v>
       </c>
       <c r="P41" s="13">
-        <v>665609</v>
+        <v>665625</v>
       </c>
       <c r="Q41" s="14">
         <f t="shared" si="5"/>
-        <v>0.95001227463204652</v>
+        <v>0.95003511115678418</v>
       </c>
       <c r="R41" s="12">
         <v>688720</v>
@@ -6144,14 +6147,14 @@
       </c>
       <c r="T41" s="15">
         <f t="shared" si="6"/>
-        <v>252590</v>
+        <v>252609</v>
       </c>
       <c r="U41" s="13">
-        <v>648463</v>
+        <v>648482</v>
       </c>
       <c r="V41" s="14">
         <f t="shared" si="7"/>
-        <v>0.94154808920896738</v>
+        <v>0.94157567661749331</v>
       </c>
       <c r="W41" s="12">
         <v>702649</v>
@@ -6161,14 +6164,14 @@
       </c>
       <c r="Y41" s="15">
         <f t="shared" si="8"/>
-        <v>224582</v>
+        <v>224606</v>
       </c>
       <c r="Z41" s="13">
-        <v>653147</v>
+        <v>653171</v>
       </c>
       <c r="AA41" s="14">
         <f t="shared" si="9"/>
-        <v>0.92954946210696954</v>
+        <v>0.92958361856346483</v>
       </c>
       <c r="AB41" s="12">
         <v>712131</v>
@@ -6178,14 +6181,14 @@
       </c>
       <c r="AD41" s="15">
         <f t="shared" si="10"/>
-        <v>204635</v>
-      </c>
-      <c r="AE41" s="13">
-        <v>658347</v>
+        <v>204657</v>
+      </c>
+      <c r="AE41" s="22">
+        <v>658369</v>
       </c>
       <c r="AF41" s="14">
         <f t="shared" si="11"/>
-        <v>0.92447456998782529</v>
+        <v>0.92450546318022953</v>
       </c>
       <c r="AG41" s="12">
         <v>722496</v>
@@ -6195,14 +6198,14 @@
       </c>
       <c r="AI41" s="15">
         <f t="shared" si="12"/>
-        <v>206284</v>
+        <v>206304</v>
       </c>
       <c r="AJ41" s="13">
-        <v>665028</v>
+        <v>665048</v>
       </c>
       <c r="AK41" s="14">
         <f t="shared" si="13"/>
-        <v>0.92045907520595271</v>
+        <v>0.92048675702010807</v>
       </c>
       <c r="AL41" s="12">
         <v>737038</v>
@@ -6212,14 +6215,14 @@
       </c>
       <c r="AN41" s="15">
         <f t="shared" si="14"/>
-        <v>213583</v>
+        <v>213606</v>
       </c>
       <c r="AO41" s="13">
-        <v>675098</v>
+        <v>675121</v>
       </c>
       <c r="AP41" s="14">
         <f t="shared" si="15"/>
-        <v>0.91596091381991163</v>
+        <v>0.91599211980929074</v>
       </c>
       <c r="AQ41" s="12">
         <v>750910</v>
@@ -6229,14 +6232,14 @@
       </c>
       <c r="AS41" s="15">
         <f t="shared" si="16"/>
-        <v>230857</v>
+        <v>230884</v>
       </c>
       <c r="AT41" s="13">
-        <v>684714</v>
+        <v>684741</v>
       </c>
       <c r="AU41" s="14">
         <f t="shared" si="17"/>
-        <v>0.91184562730553598</v>
+        <v>0.91188158367847016</v>
       </c>
     </row>
     <row r="42" spans="1:47" x14ac:dyDescent="0.3">
@@ -6341,7 +6344,7 @@
         <f t="shared" si="10"/>
         <v>5476</v>
       </c>
-      <c r="AE42" s="13">
+      <c r="AE42" s="22">
         <v>15470</v>
       </c>
       <c r="AF42" s="14">
@@ -6502,7 +6505,7 @@
         <f t="shared" si="10"/>
         <v>2360</v>
       </c>
-      <c r="AE43" s="13">
+      <c r="AE43" s="22">
         <v>3242</v>
       </c>
       <c r="AF43" s="14">
@@ -6593,14 +6596,14 @@
       </c>
       <c r="J44" s="15">
         <f t="shared" si="2"/>
-        <v>148223</v>
+        <v>148224</v>
       </c>
       <c r="K44" s="13">
-        <v>211520</v>
+        <v>211521</v>
       </c>
       <c r="L44" s="14">
         <f t="shared" si="3"/>
-        <v>0.94487626194943264</v>
+        <v>0.94488072902707054</v>
       </c>
       <c r="M44" s="12">
         <v>234895</v>
@@ -6610,14 +6613,14 @@
       </c>
       <c r="O44" s="15">
         <f t="shared" si="4"/>
-        <v>131884</v>
+        <v>131885</v>
       </c>
       <c r="P44" s="13">
-        <v>222519</v>
+        <v>222520</v>
       </c>
       <c r="Q44" s="14">
         <f t="shared" si="5"/>
-        <v>0.94731262904702096</v>
+        <v>0.94731688626833266</v>
       </c>
       <c r="R44" s="12">
         <v>230496</v>
@@ -6627,14 +6630,14 @@
       </c>
       <c r="T44" s="15">
         <f t="shared" si="6"/>
-        <v>105124</v>
+        <v>105125</v>
       </c>
       <c r="U44" s="13">
-        <v>216179</v>
+        <v>216180</v>
       </c>
       <c r="V44" s="14">
         <f t="shared" si="7"/>
-        <v>0.93788612383728998</v>
+        <v>0.93789046230737194</v>
       </c>
       <c r="W44" s="12">
         <v>237791</v>
@@ -6644,14 +6647,14 @@
       </c>
       <c r="Y44" s="15">
         <f t="shared" si="8"/>
-        <v>96009</v>
+        <v>96010</v>
       </c>
       <c r="Z44" s="13">
-        <v>219042</v>
+        <v>219043</v>
       </c>
       <c r="AA44" s="14">
         <f t="shared" si="9"/>
-        <v>0.92115344987825443</v>
+        <v>0.92115765525188087</v>
       </c>
       <c r="AB44" s="12">
         <v>241225</v>
@@ -6661,14 +6664,14 @@
       </c>
       <c r="AD44" s="15">
         <f t="shared" si="10"/>
-        <v>83975</v>
-      </c>
-      <c r="AE44" s="13">
-        <v>221202</v>
+        <v>83976</v>
+      </c>
+      <c r="AE44" s="22">
+        <v>221203</v>
       </c>
       <c r="AF44" s="14">
         <f t="shared" si="11"/>
-        <v>0.91699450720281894</v>
+        <v>0.91699865271012537</v>
       </c>
       <c r="AG44" s="12">
         <v>247652</v>
@@ -6678,14 +6681,14 @@
       </c>
       <c r="AI44" s="15">
         <f t="shared" si="12"/>
-        <v>88226</v>
+        <v>88227</v>
       </c>
       <c r="AJ44" s="13">
-        <v>225802</v>
+        <v>225803</v>
       </c>
       <c r="AK44" s="14">
         <f t="shared" si="13"/>
-        <v>0.91177135658100883</v>
+        <v>0.91177539450519274</v>
       </c>
       <c r="AL44" s="12">
         <v>253873</v>
@@ -6695,14 +6698,14 @@
       </c>
       <c r="AN44" s="15">
         <f t="shared" si="14"/>
-        <v>88358</v>
+        <v>88360</v>
       </c>
       <c r="AO44" s="13">
-        <v>230439</v>
+        <v>230441</v>
       </c>
       <c r="AP44" s="14">
         <f t="shared" si="15"/>
-        <v>0.90769400448255622</v>
+        <v>0.90770188243728167</v>
       </c>
       <c r="AQ44" s="12">
         <v>259182</v>
@@ -6712,14 +6715,14 @@
       </c>
       <c r="AS44" s="15">
         <f t="shared" si="16"/>
-        <v>94052</v>
+        <v>94053</v>
       </c>
       <c r="AT44" s="13">
-        <v>234439</v>
+        <v>234440</v>
       </c>
       <c r="AU44" s="14">
         <f t="shared" si="17"/>
-        <v>0.90453426549683236</v>
+        <v>0.90453812378946064</v>
       </c>
     </row>
     <row r="45" spans="1:47" x14ac:dyDescent="0.3">
@@ -6788,14 +6791,14 @@
       </c>
       <c r="T45" s="15">
         <f t="shared" si="6"/>
-        <v>79304</v>
+        <v>79306</v>
       </c>
       <c r="U45" s="13">
-        <v>198232</v>
+        <v>198234</v>
       </c>
       <c r="V45" s="14">
         <f t="shared" si="7"/>
-        <v>0.95003306846610247</v>
+        <v>0.95004265352874084</v>
       </c>
       <c r="W45" s="12">
         <v>214751</v>
@@ -6805,14 +6808,14 @@
       </c>
       <c r="Y45" s="15">
         <f t="shared" si="8"/>
-        <v>70883</v>
+        <v>70885</v>
       </c>
       <c r="Z45" s="13">
-        <v>200308</v>
+        <v>200310</v>
       </c>
       <c r="AA45" s="14">
         <f t="shared" si="9"/>
-        <v>0.93274536556290777</v>
+        <v>0.93275467867437167</v>
       </c>
       <c r="AB45" s="12">
         <v>215764</v>
@@ -6822,14 +6825,14 @@
       </c>
       <c r="AD45" s="15">
         <f t="shared" si="10"/>
-        <v>61334</v>
-      </c>
-      <c r="AE45" s="13">
-        <v>201488</v>
+        <v>61336</v>
+      </c>
+      <c r="AE45" s="22">
+        <v>201490</v>
       </c>
       <c r="AF45" s="14">
         <f t="shared" si="11"/>
-        <v>0.93383511614541814</v>
+        <v>0.93384438553234084</v>
       </c>
       <c r="AG45" s="12">
         <v>219257</v>
@@ -6839,14 +6842,14 @@
       </c>
       <c r="AI45" s="15">
         <f t="shared" si="12"/>
-        <v>62903</v>
+        <v>62906</v>
       </c>
       <c r="AJ45" s="13">
-        <v>204125</v>
+        <v>204128</v>
       </c>
       <c r="AK45" s="14">
         <f t="shared" si="13"/>
-        <v>0.93098509967754739</v>
+        <v>0.93099878225096577</v>
       </c>
       <c r="AL45" s="12">
         <v>223004</v>
@@ -6856,14 +6859,14 @@
       </c>
       <c r="AN45" s="15">
         <f t="shared" si="14"/>
-        <v>68856</v>
+        <v>68859</v>
       </c>
       <c r="AO45" s="13">
-        <v>206977</v>
+        <v>206980</v>
       </c>
       <c r="AP45" s="14">
         <f t="shared" si="15"/>
-        <v>0.92813133396710368</v>
+        <v>0.92814478664059841</v>
       </c>
       <c r="AQ45" s="12">
         <v>226630</v>
@@ -6873,14 +6876,14 @@
       </c>
       <c r="AS45" s="15">
         <f t="shared" si="16"/>
-        <v>81548</v>
+        <v>81551</v>
       </c>
       <c r="AT45" s="13">
-        <v>210517</v>
+        <v>210520</v>
       </c>
       <c r="AU45" s="14">
         <f t="shared" si="17"/>
-        <v>0.9289017341040462</v>
+        <v>0.92891497153951375</v>
       </c>
     </row>
     <row r="46" spans="1:47" x14ac:dyDescent="0.3">
@@ -6974,7 +6977,7 @@
       <c r="AD46" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="AE46" s="13">
+      <c r="AE46" s="22">
         <v>0</v>
       </c>
       <c r="AF46" s="16" t="s">
@@ -7126,7 +7129,7 @@
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
-      <c r="AE47" s="13">
+      <c r="AE47" s="22">
         <v>35</v>
       </c>
       <c r="AF47" s="14">
@@ -7200,15 +7203,15 @@
       </c>
       <c r="E48" s="18">
         <f t="shared" si="0"/>
-        <v>2850792</v>
+        <v>2850818</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>6617055</v>
+        <v>6617081</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" ref="G48" si="18">F48/C48</f>
-        <v>0.97545045845200817</v>
+        <v>0.97545429123138205</v>
       </c>
       <c r="H48" s="17">
         <f>SUM(H10:H47)</f>
@@ -7220,15 +7223,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>4422284</v>
+        <v>4422312</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>7216043</v>
+        <v>7216071</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.96506746738971405</v>
+        <v>0.96507121208595359</v>
       </c>
       <c r="M48" s="17">
         <f>SUM(M10:M47)</f>
@@ -7240,15 +7243,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>3706375</v>
+        <v>3706413</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>7574158</v>
+        <v>7574196</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.96645683821576955</v>
+        <v>0.96646168698705903</v>
       </c>
       <c r="R48" s="17">
         <f>SUM(R10:R47)</f>
@@ -7260,15 +7263,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>2999157</v>
+        <v>2999198</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>7326881</v>
+        <v>7326922</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.95805389640846217</v>
+        <v>0.95805925751774623</v>
       </c>
       <c r="W48" s="17">
         <f>SUM(W10:W47)</f>
@@ -7280,15 +7283,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2552708</v>
+        <v>2552751</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>7437144</v>
+        <v>7437187</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.94833346722211387</v>
+        <v>0.9483389502864582</v>
       </c>
       <c r="AB48" s="17">
         <f>SUM(AB10:AB47)</f>
@@ -7300,15 +7303,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>2124111</v>
+        <v>2124149</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>7529860</v>
+        <v>7529898</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.94467157687561565</v>
+        <v>0.94467634423117364</v>
       </c>
       <c r="AG48" s="17">
         <f>SUM(AG10:AG47)</f>
@@ -7320,15 +7323,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2280211</v>
+        <v>2280244</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7660785</v>
+        <v>7660818</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.94074676341366192</v>
+        <v>0.94075081582385134</v>
       </c>
       <c r="AL48" s="17">
         <f>SUM(AL10:AL47)</f>
@@ -7340,15 +7343,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2359934</v>
+        <v>2359971</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>7795734</v>
+        <v>7795771</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.9379233792958741</v>
+        <v>0.93792783085425646</v>
       </c>
       <c r="AQ48" s="17">
         <f>SUM(AQ10:AQ47)</f>
@@ -7360,32 +7363,32 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2655095</v>
+        <v>2655141</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>7915004</v>
+        <v>7915050</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.93606285892493202</v>
+        <v>0.93606829908535527</v>
       </c>
     </row>
-    <row r="55" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A55" s="25" t="s">
+    <row r="57" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="A57" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="4"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="4"/>
     </row>
-    <row r="56" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="AV56">
+    <row r="58" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="AV58">
         <v>24985627</v>
       </c>
-      <c r="AW56">
+      <c r="AW58">
         <v>66107624</v>
       </c>
     </row>
@@ -7394,7 +7397,7 @@
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="W8:AA8"/>

--- a/gstdatabase/GSTR-3B-2017-2018.xlsx
+++ b/gstdatabase/GSTR-3B-2017-2018.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DD5A9F-B6DE-475F-9457-4358F1ED7430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3A4EB7-D71E-4C70-BDE9-9D7C2193E7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -1105,14 +1105,14 @@
       </c>
       <c r="E10" s="12">
         <f>F10-D10</f>
-        <v>22948</v>
+        <v>22949</v>
       </c>
       <c r="F10" s="13">
-        <v>49449</v>
+        <v>49450</v>
       </c>
       <c r="G10" s="14">
         <f>F10/C10</f>
-        <v>0.94269373748927654</v>
+        <v>0.94271280144886094</v>
       </c>
       <c r="H10" s="12">
         <v>58371</v>
@@ -1122,14 +1122,14 @@
       </c>
       <c r="J10" s="15">
         <f>K10-I10</f>
-        <v>35123</v>
+        <v>35124</v>
       </c>
       <c r="K10" s="13">
-        <v>55657</v>
+        <v>55658</v>
       </c>
       <c r="L10" s="14">
         <f>K10/H10</f>
-        <v>0.95350430864641689</v>
+        <v>0.95352144044131504</v>
       </c>
       <c r="M10" s="12">
         <v>62528</v>
@@ -1139,14 +1139,14 @@
       </c>
       <c r="O10" s="15">
         <f>P10-N10</f>
-        <v>31411</v>
+        <v>31412</v>
       </c>
       <c r="P10" s="13">
-        <v>59582</v>
+        <v>59583</v>
       </c>
       <c r="Q10" s="14">
         <f>P10/M10</f>
-        <v>0.95288510747185262</v>
+        <v>0.95290110030706243</v>
       </c>
       <c r="R10" s="12">
         <v>62319</v>
@@ -1766,14 +1766,14 @@
       </c>
       <c r="J14" s="15">
         <f t="shared" si="2"/>
-        <v>62073</v>
+        <v>62074</v>
       </c>
       <c r="K14" s="13">
-        <v>88851</v>
+        <v>88852</v>
       </c>
       <c r="L14" s="14">
         <f t="shared" si="3"/>
-        <v>0.93680215087774787</v>
+        <v>0.93681269439612003</v>
       </c>
       <c r="M14" s="12">
         <v>100078</v>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="O14" s="15">
         <f t="shared" si="4"/>
-        <v>56720</v>
+        <v>56722</v>
       </c>
       <c r="P14" s="13">
-        <v>93506</v>
+        <v>93508</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="5"/>
-        <v>0.93433122164711524</v>
+        <v>0.9343512060592738</v>
       </c>
       <c r="R14" s="12">
         <v>94880</v>
@@ -1800,14 +1800,14 @@
       </c>
       <c r="T14" s="15">
         <f t="shared" si="6"/>
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="U14" s="13">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="V14" s="14">
         <f t="shared" si="7"/>
-        <v>0.92354553119730187</v>
+        <v>0.92355607082630686</v>
       </c>
       <c r="W14" s="12">
         <v>97711</v>
@@ -2088,14 +2088,14 @@
       </c>
       <c r="J16" s="15">
         <f t="shared" si="2"/>
-        <v>276671</v>
+        <v>276672</v>
       </c>
       <c r="K16" s="13">
-        <v>491543</v>
+        <v>491544</v>
       </c>
       <c r="L16" s="14">
         <f t="shared" si="3"/>
-        <v>0.99830212092717197</v>
+        <v>0.9983041518830007</v>
       </c>
       <c r="M16" s="12">
         <v>521051</v>
@@ -2249,14 +2249,14 @@
       </c>
       <c r="J17" s="15">
         <f t="shared" si="2"/>
-        <v>230401</v>
+        <v>230403</v>
       </c>
       <c r="K17" s="13">
-        <v>410476</v>
+        <v>410478</v>
       </c>
       <c r="L17" s="14">
         <f t="shared" si="3"/>
-        <v>0.97051862535317834</v>
+        <v>0.9705233541004149</v>
       </c>
       <c r="M17" s="12">
         <v>435929</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="O17" s="15">
         <f t="shared" si="4"/>
-        <v>200005</v>
+        <v>200006</v>
       </c>
       <c r="P17" s="13">
-        <v>425347</v>
+        <v>425348</v>
       </c>
       <c r="Q17" s="14">
         <f t="shared" si="5"/>
-        <v>0.97572540482509762</v>
+        <v>0.97572769877663568</v>
       </c>
       <c r="R17" s="12">
         <v>418736</v>
@@ -2283,14 +2283,14 @@
       </c>
       <c r="T17" s="15">
         <f t="shared" si="6"/>
-        <v>153459</v>
+        <v>153460</v>
       </c>
       <c r="U17" s="13">
-        <v>405791</v>
+        <v>405792</v>
       </c>
       <c r="V17" s="14">
         <f t="shared" si="7"/>
-        <v>0.96908553360589966</v>
+        <v>0.96908792174544345</v>
       </c>
       <c r="W17" s="12">
         <v>427452</v>
@@ -2300,14 +2300,14 @@
       </c>
       <c r="Y17" s="15">
         <f t="shared" si="8"/>
-        <v>127012</v>
+        <v>127013</v>
       </c>
       <c r="Z17" s="13">
-        <v>411160</v>
+        <v>411161</v>
       </c>
       <c r="AA17" s="14">
         <f t="shared" si="9"/>
-        <v>0.96188577898805017</v>
+        <v>0.96188811843201105</v>
       </c>
       <c r="AB17" s="12">
         <v>433360</v>
@@ -2317,14 +2317,14 @@
       </c>
       <c r="AD17" s="15">
         <f t="shared" si="10"/>
-        <v>100708</v>
+        <v>100709</v>
       </c>
       <c r="AE17" s="22">
-        <v>415533</v>
+        <v>415534</v>
       </c>
       <c r="AF17" s="14">
         <f t="shared" si="11"/>
-        <v>0.95886330071995574</v>
+        <v>0.95886560827026024</v>
       </c>
       <c r="AG17" s="12">
         <v>442318</v>
@@ -2334,14 +2334,14 @@
       </c>
       <c r="AI17" s="15">
         <f t="shared" si="12"/>
-        <v>112660</v>
+        <v>112661</v>
       </c>
       <c r="AJ17" s="13">
-        <v>422351</v>
+        <v>422352</v>
       </c>
       <c r="AK17" s="14">
         <f t="shared" si="13"/>
-        <v>0.95485826938989593</v>
+        <v>0.95486053020677431</v>
       </c>
       <c r="AL17" s="12">
         <v>449574</v>
@@ -2351,14 +2351,14 @@
       </c>
       <c r="AN17" s="15">
         <f t="shared" si="14"/>
-        <v>117851</v>
+        <v>117852</v>
       </c>
       <c r="AO17" s="13">
-        <v>428786</v>
+        <v>428787</v>
       </c>
       <c r="AP17" s="14">
         <f t="shared" si="15"/>
-        <v>0.95376067121319297</v>
+        <v>0.95376289554111227</v>
       </c>
       <c r="AQ17" s="12">
         <v>455889</v>
@@ -2427,14 +2427,14 @@
       </c>
       <c r="O18" s="15">
         <f t="shared" si="4"/>
-        <v>403669</v>
+        <v>403670</v>
       </c>
       <c r="P18" s="13">
-        <v>850384</v>
+        <v>850385</v>
       </c>
       <c r="Q18" s="14">
         <f t="shared" si="5"/>
-        <v>0.95779495774089496</v>
+        <v>0.95779608404966576</v>
       </c>
       <c r="R18" s="12">
         <v>809536</v>
@@ -2444,14 +2444,14 @@
       </c>
       <c r="T18" s="15">
         <f t="shared" si="6"/>
-        <v>282966</v>
+        <v>282967</v>
       </c>
       <c r="U18" s="13">
-        <v>769618</v>
+        <v>769619</v>
       </c>
       <c r="V18" s="14">
         <f t="shared" si="7"/>
-        <v>0.95069027195825762</v>
+        <v>0.95069150723377338</v>
       </c>
       <c r="W18" s="12">
         <v>834136</v>
@@ -2529,14 +2529,14 @@
       </c>
       <c r="AS18" s="15">
         <f t="shared" si="16"/>
-        <v>225451</v>
+        <v>225452</v>
       </c>
       <c r="AT18" s="13">
-        <v>845571</v>
+        <v>845572</v>
       </c>
       <c r="AU18" s="14">
         <f t="shared" si="17"/>
-        <v>0.92598441235316087</v>
+        <v>0.92598550745269992</v>
       </c>
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.3">
@@ -2690,14 +2690,14 @@
       </c>
       <c r="AS19" s="15">
         <f t="shared" si="16"/>
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="AT19" s="13">
-        <v>209746</v>
+        <v>209747</v>
       </c>
       <c r="AU19" s="14">
         <f t="shared" si="17"/>
-        <v>0.87855039561700754</v>
+        <v>0.87855458425657929</v>
       </c>
     </row>
     <row r="20" spans="1:47" x14ac:dyDescent="0.3">
@@ -3495,14 +3495,14 @@
       </c>
       <c r="AS24" s="15">
         <f t="shared" si="16"/>
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="AT24" s="13">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="AU24" s="14">
         <f t="shared" si="17"/>
-        <v>0.83596837944664026</v>
+        <v>0.83621541501976282</v>
       </c>
     </row>
     <row r="25" spans="1:47" x14ac:dyDescent="0.3">
@@ -3944,14 +3944,14 @@
       </c>
       <c r="AI27" s="15">
         <f t="shared" si="12"/>
-        <v>47573</v>
+        <v>47574</v>
       </c>
       <c r="AJ27" s="13">
-        <v>98142</v>
+        <v>98143</v>
       </c>
       <c r="AK27" s="14">
         <f t="shared" si="13"/>
-        <v>0.84597879493147143</v>
+        <v>0.84598741487802775</v>
       </c>
       <c r="AL27" s="12">
         <v>119071</v>
@@ -4037,14 +4037,14 @@
       </c>
       <c r="O28" s="15">
         <f t="shared" si="4"/>
-        <v>195213</v>
+        <v>195214</v>
       </c>
       <c r="P28" s="13">
-        <v>401460</v>
+        <v>401461</v>
       </c>
       <c r="Q28" s="14">
         <f t="shared" si="5"/>
-        <v>0.96497616764135363</v>
+        <v>0.96497857130838804</v>
       </c>
       <c r="R28" s="12">
         <v>422302</v>
@@ -4054,14 +4054,14 @@
       </c>
       <c r="T28" s="15">
         <f t="shared" si="6"/>
-        <v>159562</v>
+        <v>159563</v>
       </c>
       <c r="U28" s="13">
-        <v>403034</v>
+        <v>403035</v>
       </c>
       <c r="V28" s="14">
         <f t="shared" si="7"/>
-        <v>0.95437388409242674</v>
+        <v>0.95437625206605703</v>
       </c>
       <c r="W28" s="12">
         <v>436034</v>
@@ -4681,14 +4681,14 @@
       </c>
       <c r="O32" s="15">
         <f t="shared" si="4"/>
-        <v>166100</v>
+        <v>166101</v>
       </c>
       <c r="P32" s="13">
-        <v>280922</v>
+        <v>280923</v>
       </c>
       <c r="Q32" s="14">
         <f t="shared" si="5"/>
-        <v>0.96752884449801968</v>
+        <v>0.96753228861718621</v>
       </c>
       <c r="R32" s="12">
         <v>274212</v>
@@ -4698,14 +4698,14 @@
       </c>
       <c r="T32" s="15">
         <f t="shared" si="6"/>
-        <v>126730</v>
+        <v>126731</v>
       </c>
       <c r="U32" s="13">
-        <v>262498</v>
+        <v>262499</v>
       </c>
       <c r="V32" s="14">
         <f t="shared" si="7"/>
-        <v>0.95728122766326784</v>
+        <v>0.95728487447668231</v>
       </c>
       <c r="W32" s="12">
         <v>281366</v>
@@ -4715,14 +4715,14 @@
       </c>
       <c r="Y32" s="15">
         <f t="shared" si="8"/>
-        <v>101594</v>
+        <v>101595</v>
       </c>
       <c r="Z32" s="13">
-        <v>265434</v>
+        <v>265435</v>
       </c>
       <c r="AA32" s="14">
         <f t="shared" si="9"/>
-        <v>0.94337624304286938</v>
+        <v>0.94337979713256048</v>
       </c>
       <c r="AB32" s="12">
         <v>286853</v>
@@ -4825,14 +4825,14 @@
       </c>
       <c r="J33" s="15">
         <f t="shared" si="2"/>
-        <v>381812</v>
+        <v>381815</v>
       </c>
       <c r="K33" s="13">
-        <v>630528</v>
+        <v>630531</v>
       </c>
       <c r="L33" s="14">
         <f t="shared" si="3"/>
-        <v>0.98265431117511193</v>
+        <v>0.98265898656293538</v>
       </c>
       <c r="M33" s="12">
         <v>682019</v>
@@ -4859,14 +4859,14 @@
       </c>
       <c r="T33" s="15">
         <f t="shared" si="6"/>
-        <v>271305</v>
+        <v>271306</v>
       </c>
       <c r="U33" s="13">
-        <v>662050</v>
+        <v>662051</v>
       </c>
       <c r="V33" s="14">
         <f t="shared" si="7"/>
-        <v>0.98303574742937749</v>
+        <v>0.98303723226548867</v>
       </c>
       <c r="W33" s="12">
         <v>688205</v>
@@ -4876,14 +4876,14 @@
       </c>
       <c r="Y33" s="15">
         <f t="shared" si="8"/>
-        <v>206622</v>
+        <v>206624</v>
       </c>
       <c r="Z33" s="13">
-        <v>674446</v>
+        <v>674448</v>
       </c>
       <c r="AA33" s="14">
         <f t="shared" si="9"/>
-        <v>0.98000741058260255</v>
+        <v>0.98001031669342709</v>
       </c>
       <c r="AB33" s="12">
         <v>698869</v>
@@ -4893,14 +4893,14 @@
       </c>
       <c r="AD33" s="15">
         <f t="shared" si="10"/>
-        <v>160026</v>
+        <v>160028</v>
       </c>
       <c r="AE33" s="22">
-        <v>684446</v>
+        <v>684448</v>
       </c>
       <c r="AF33" s="14">
         <f t="shared" si="11"/>
-        <v>0.97936236977173119</v>
+        <v>0.97936523153838562</v>
       </c>
       <c r="AG33" s="12">
         <v>712579</v>
@@ -4910,14 +4910,14 @@
       </c>
       <c r="AI33" s="15">
         <f t="shared" si="12"/>
-        <v>175970</v>
+        <v>175971</v>
       </c>
       <c r="AJ33" s="13">
-        <v>696869</v>
+        <v>696870</v>
       </c>
       <c r="AK33" s="14">
         <f t="shared" si="13"/>
-        <v>0.97795332166679061</v>
+        <v>0.97795472501996272</v>
       </c>
       <c r="AL33" s="12">
         <v>723682</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="O36" s="15">
         <f t="shared" si="4"/>
-        <v>484933</v>
+        <v>484934</v>
       </c>
       <c r="P36" s="13">
-        <v>1042170</v>
+        <v>1042171</v>
       </c>
       <c r="Q36" s="14">
         <f t="shared" si="5"/>
-        <v>0.98269716742729984</v>
+        <v>0.982698110360955</v>
       </c>
       <c r="R36" s="12">
         <v>1054857</v>
@@ -5342,14 +5342,14 @@
       </c>
       <c r="T36" s="15">
         <f t="shared" si="6"/>
-        <v>445768</v>
+        <v>445769</v>
       </c>
       <c r="U36" s="13">
-        <v>1031366</v>
+        <v>1031367</v>
       </c>
       <c r="V36" s="14">
         <f t="shared" si="7"/>
-        <v>0.97773063078692179</v>
+        <v>0.97773157878271655</v>
       </c>
       <c r="W36" s="12">
         <v>1076657</v>
@@ -5452,14 +5452,14 @@
       </c>
       <c r="E37" s="12">
         <f t="shared" si="0"/>
-        <v>234915</v>
+        <v>234916</v>
       </c>
       <c r="F37" s="13">
-        <v>499885</v>
+        <v>499886</v>
       </c>
       <c r="G37" s="14">
         <f t="shared" si="1"/>
-        <v>0.99300367297236625</v>
+        <v>0.99300565943659902</v>
       </c>
       <c r="H37" s="12">
         <v>530355</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="J37" s="15">
         <f t="shared" si="2"/>
-        <v>309552</v>
+        <v>309554</v>
       </c>
       <c r="K37" s="13">
-        <v>519224</v>
+        <v>519226</v>
       </c>
       <c r="L37" s="14">
         <f t="shared" si="3"/>
-        <v>0.97901217109294714</v>
+        <v>0.97901594215195487</v>
       </c>
       <c r="M37" s="12">
         <v>553919</v>
@@ -5486,14 +5486,14 @@
       </c>
       <c r="O37" s="15">
         <f t="shared" si="4"/>
-        <v>252340</v>
+        <v>252342</v>
       </c>
       <c r="P37" s="13">
-        <v>538156</v>
+        <v>538158</v>
       </c>
       <c r="Q37" s="14">
         <f t="shared" si="5"/>
-        <v>0.97154277069391015</v>
+        <v>0.97154638133012228</v>
       </c>
       <c r="R37" s="12">
         <v>537199</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="T37" s="15">
         <f t="shared" si="6"/>
-        <v>196448</v>
+        <v>196451</v>
       </c>
       <c r="U37" s="13">
-        <v>514128</v>
+        <v>514131</v>
       </c>
       <c r="V37" s="14">
         <f t="shared" si="7"/>
-        <v>0.95705315907140553</v>
+        <v>0.95705874359408716</v>
       </c>
       <c r="W37" s="12">
         <v>549345</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="Y37" s="15">
         <f t="shared" si="8"/>
-        <v>170960</v>
+        <v>170962</v>
       </c>
       <c r="Z37" s="13">
-        <v>518612</v>
+        <v>518614</v>
       </c>
       <c r="AA37" s="14">
         <f t="shared" si="9"/>
-        <v>0.94405519300257579</v>
+        <v>0.94405883370195409</v>
       </c>
       <c r="AB37" s="12">
         <v>556414</v>
@@ -5537,14 +5537,14 @@
       </c>
       <c r="AD37" s="15">
         <f t="shared" si="10"/>
-        <v>142525</v>
+        <v>142530</v>
       </c>
       <c r="AE37" s="22">
-        <v>523078</v>
+        <v>523083</v>
       </c>
       <c r="AF37" s="14">
         <f t="shared" si="11"/>
-        <v>0.94008777636795626</v>
+        <v>0.94009676248261187</v>
       </c>
       <c r="AG37" s="12">
         <v>568190</v>
@@ -5554,14 +5554,14 @@
       </c>
       <c r="AI37" s="15">
         <f t="shared" si="12"/>
-        <v>151238</v>
+        <v>151242</v>
       </c>
       <c r="AJ37" s="13">
-        <v>531700</v>
+        <v>531704</v>
       </c>
       <c r="AK37" s="14">
         <f t="shared" si="13"/>
-        <v>0.93577852478924306</v>
+        <v>0.93578556468786844</v>
       </c>
       <c r="AL37" s="12">
         <v>579378</v>
@@ -5571,14 +5571,14 @@
       </c>
       <c r="AN37" s="15">
         <f t="shared" si="14"/>
-        <v>159380</v>
+        <v>159383</v>
       </c>
       <c r="AO37" s="13">
-        <v>539979</v>
+        <v>539982</v>
       </c>
       <c r="AP37" s="14">
         <f t="shared" si="15"/>
-        <v>0.93199776311837867</v>
+        <v>0.93200294108509474</v>
       </c>
       <c r="AQ37" s="12">
         <v>590015</v>
@@ -5588,14 +5588,14 @@
       </c>
       <c r="AS37" s="15">
         <f t="shared" si="16"/>
-        <v>175707</v>
+        <v>175710</v>
       </c>
       <c r="AT37" s="13">
-        <v>547810</v>
+        <v>547813</v>
       </c>
       <c r="AU37" s="14">
         <f t="shared" si="17"/>
-        <v>0.92846792030711078</v>
+        <v>0.92847300492360363</v>
       </c>
     </row>
     <row r="38" spans="1:47" x14ac:dyDescent="0.3">
@@ -6020,14 +6020,14 @@
       </c>
       <c r="AD40" s="15">
         <f t="shared" si="10"/>
-        <v>78436</v>
+        <v>78437</v>
       </c>
       <c r="AE40" s="22">
-        <v>228690</v>
+        <v>228691</v>
       </c>
       <c r="AF40" s="14">
         <f t="shared" si="11"/>
-        <v>0.97416870426063029</v>
+        <v>0.97417296403895137</v>
       </c>
       <c r="AG40" s="12">
         <v>238699</v>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="AS40" s="15">
         <f t="shared" si="16"/>
-        <v>108295</v>
+        <v>108296</v>
       </c>
       <c r="AT40" s="13">
-        <v>238385</v>
+        <v>238386</v>
       </c>
       <c r="AU40" s="14">
         <f t="shared" si="17"/>
-        <v>0.96998710128946419</v>
+        <v>0.96999117028332404</v>
       </c>
     </row>
     <row r="41" spans="1:47" x14ac:dyDescent="0.3">
@@ -6096,14 +6096,14 @@
       </c>
       <c r="E41" s="12">
         <f t="shared" si="0"/>
-        <v>291295</v>
+        <v>291301</v>
       </c>
       <c r="F41" s="13">
-        <v>603812</v>
+        <v>603818</v>
       </c>
       <c r="G41" s="14">
         <f t="shared" si="1"/>
-        <v>0.96630637608703307</v>
+        <v>0.96631597814571446</v>
       </c>
       <c r="H41" s="12">
         <v>673862</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="J41" s="15">
         <f t="shared" si="2"/>
-        <v>440797</v>
+        <v>440804</v>
       </c>
       <c r="K41" s="13">
-        <v>643241</v>
+        <v>643248</v>
       </c>
       <c r="L41" s="14">
         <f t="shared" si="3"/>
-        <v>0.95455894530334107</v>
+        <v>0.95456933318691362</v>
       </c>
       <c r="M41" s="12">
         <v>700632</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="O41" s="15">
         <f t="shared" si="4"/>
-        <v>341593</v>
+        <v>341596</v>
       </c>
       <c r="P41" s="13">
-        <v>665625</v>
+        <v>665628</v>
       </c>
       <c r="Q41" s="14">
         <f t="shared" si="5"/>
-        <v>0.95003511115678418</v>
+        <v>0.95003939300517248</v>
       </c>
       <c r="R41" s="12">
         <v>688720</v>
@@ -6147,14 +6147,14 @@
       </c>
       <c r="T41" s="15">
         <f t="shared" si="6"/>
-        <v>252609</v>
+        <v>252613</v>
       </c>
       <c r="U41" s="13">
-        <v>648482</v>
+        <v>648486</v>
       </c>
       <c r="V41" s="14">
         <f t="shared" si="7"/>
-        <v>0.94157567661749331</v>
+        <v>0.94158148449297252</v>
       </c>
       <c r="W41" s="12">
         <v>702649</v>
@@ -6164,14 +6164,14 @@
       </c>
       <c r="Y41" s="15">
         <f t="shared" si="8"/>
-        <v>224606</v>
+        <v>224611</v>
       </c>
       <c r="Z41" s="13">
-        <v>653171</v>
+        <v>653176</v>
       </c>
       <c r="AA41" s="14">
         <f t="shared" si="9"/>
-        <v>0.92958361856346483</v>
+        <v>0.92959073449190133</v>
       </c>
       <c r="AB41" s="12">
         <v>712131</v>
@@ -6181,14 +6181,14 @@
       </c>
       <c r="AD41" s="15">
         <f t="shared" si="10"/>
-        <v>204657</v>
+        <v>204659</v>
       </c>
       <c r="AE41" s="22">
-        <v>658369</v>
+        <v>658371</v>
       </c>
       <c r="AF41" s="14">
         <f t="shared" si="11"/>
-        <v>0.92450546318022953</v>
+        <v>0.92450827165226623</v>
       </c>
       <c r="AG41" s="12">
         <v>722496</v>
@@ -6198,14 +6198,14 @@
       </c>
       <c r="AI41" s="15">
         <f t="shared" si="12"/>
-        <v>206304</v>
+        <v>206306</v>
       </c>
       <c r="AJ41" s="13">
-        <v>665048</v>
+        <v>665050</v>
       </c>
       <c r="AK41" s="14">
         <f t="shared" si="13"/>
-        <v>0.92048675702010807</v>
+        <v>0.92048952520152361</v>
       </c>
       <c r="AL41" s="12">
         <v>737038</v>
@@ -6215,14 +6215,14 @@
       </c>
       <c r="AN41" s="15">
         <f t="shared" si="14"/>
-        <v>213606</v>
+        <v>213610</v>
       </c>
       <c r="AO41" s="13">
-        <v>675121</v>
+        <v>675125</v>
       </c>
       <c r="AP41" s="14">
         <f t="shared" si="15"/>
-        <v>0.91599211980929074</v>
+        <v>0.91599754693787838</v>
       </c>
       <c r="AQ41" s="12">
         <v>750910</v>
@@ -6232,14 +6232,14 @@
       </c>
       <c r="AS41" s="15">
         <f t="shared" si="16"/>
-        <v>230884</v>
+        <v>230887</v>
       </c>
       <c r="AT41" s="13">
-        <v>684741</v>
+        <v>684744</v>
       </c>
       <c r="AU41" s="14">
         <f t="shared" si="17"/>
-        <v>0.91188158367847016</v>
+        <v>0.9118855788310184</v>
       </c>
     </row>
     <row r="42" spans="1:47" x14ac:dyDescent="0.3">
@@ -6291,14 +6291,14 @@
       </c>
       <c r="O42" s="15">
         <f t="shared" si="4"/>
-        <v>7401</v>
+        <v>7402</v>
       </c>
       <c r="P42" s="13">
-        <v>15424</v>
+        <v>15425</v>
       </c>
       <c r="Q42" s="14">
         <f t="shared" si="5"/>
-        <v>0.99075025693730734</v>
+        <v>0.99081449126413157</v>
       </c>
       <c r="R42" s="12">
         <v>15548</v>
@@ -6308,14 +6308,14 @@
       </c>
       <c r="T42" s="15">
         <f t="shared" si="6"/>
-        <v>6091</v>
+        <v>6092</v>
       </c>
       <c r="U42" s="13">
-        <v>15164</v>
+        <v>15165</v>
       </c>
       <c r="V42" s="14">
         <f t="shared" si="7"/>
-        <v>0.97530228968356059</v>
+        <v>0.97536660663750963</v>
       </c>
       <c r="W42" s="12">
         <v>15726</v>
@@ -6325,14 +6325,14 @@
       </c>
       <c r="Y42" s="15">
         <f t="shared" si="8"/>
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="Z42" s="13">
-        <v>15301</v>
+        <v>15302</v>
       </c>
       <c r="AA42" s="14">
         <f t="shared" si="9"/>
-        <v>0.97297469159353933</v>
+        <v>0.9730382805544957</v>
       </c>
       <c r="AB42" s="12">
         <v>15975</v>
@@ -6342,14 +6342,14 @@
       </c>
       <c r="AD42" s="15">
         <f t="shared" si="10"/>
-        <v>5476</v>
+        <v>5477</v>
       </c>
       <c r="AE42" s="22">
-        <v>15470</v>
+        <v>15471</v>
       </c>
       <c r="AF42" s="14">
         <f t="shared" si="11"/>
-        <v>0.96838810641627548</v>
+        <v>0.96845070422535207</v>
       </c>
       <c r="AG42" s="12">
         <v>16258</v>
@@ -6359,14 +6359,14 @@
       </c>
       <c r="AI42" s="15">
         <f t="shared" si="12"/>
-        <v>5605</v>
+        <v>5606</v>
       </c>
       <c r="AJ42" s="13">
-        <v>15687</v>
+        <v>15688</v>
       </c>
       <c r="AK42" s="14">
         <f t="shared" si="13"/>
-        <v>0.96487882888424159</v>
+        <v>0.96494033706482962</v>
       </c>
       <c r="AL42" s="12">
         <v>16534</v>
@@ -6376,14 +6376,14 @@
       </c>
       <c r="AN42" s="15">
         <f t="shared" si="14"/>
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="AO42" s="13">
-        <v>15952</v>
+        <v>15953</v>
       </c>
       <c r="AP42" s="14">
         <f t="shared" si="15"/>
-        <v>0.96479980645941699</v>
+        <v>0.96486028789161726</v>
       </c>
       <c r="AQ42" s="12">
         <v>16887</v>
@@ -6393,14 +6393,14 @@
       </c>
       <c r="AS42" s="15">
         <f t="shared" si="16"/>
-        <v>5920</v>
+        <v>5921</v>
       </c>
       <c r="AT42" s="13">
-        <v>16242</v>
+        <v>16243</v>
       </c>
       <c r="AU42" s="14">
         <f t="shared" si="17"/>
-        <v>0.96180493871025052</v>
+        <v>0.96186415585953688</v>
       </c>
     </row>
     <row r="43" spans="1:47" x14ac:dyDescent="0.3">
@@ -7203,15 +7203,15 @@
       </c>
       <c r="E48" s="18">
         <f t="shared" si="0"/>
-        <v>2850818</v>
+        <v>2850826</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>6617081</v>
+        <v>6617089</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" ref="G48" si="18">F48/C48</f>
-        <v>0.97545429123138205</v>
+        <v>0.97545547054811255</v>
       </c>
       <c r="H48" s="17">
         <f>SUM(H10:H47)</f>
@@ -7223,15 +7223,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>4422312</v>
+        <v>4422329</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>7216071</v>
+        <v>7216088</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.96507121208595359</v>
+        <v>0.96507348565152762</v>
       </c>
       <c r="M48" s="17">
         <f>SUM(M10:M47)</f>
@@ -7243,15 +7243,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>3706413</v>
+        <v>3706427</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>7574196</v>
+        <v>7574210</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.96646168698705903</v>
+        <v>0.96646347337648142</v>
       </c>
       <c r="R48" s="17">
         <f>SUM(R10:R47)</f>
@@ -7263,15 +7263,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>2999198</v>
+        <v>2999213</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>7326922</v>
+        <v>7326937</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.95805925751774623</v>
+        <v>0.95806121889919171</v>
       </c>
       <c r="W48" s="17">
         <f>SUM(W10:W47)</f>
@@ -7283,15 +7283,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2552751</v>
+        <v>2552763</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>7437187</v>
+        <v>7437199</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.9483389502864582</v>
+        <v>0.9483404804439497</v>
       </c>
       <c r="AB48" s="17">
         <f>SUM(AB10:AB47)</f>
@@ -7303,15 +7303,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>2124149</v>
+        <v>2124161</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>7529898</v>
+        <v>7529910</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.94467634423117364</v>
+        <v>0.94467784971187607</v>
       </c>
       <c r="AG48" s="17">
         <f>SUM(AG10:AG47)</f>
@@ -7323,15 +7323,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2280244</v>
+        <v>2280254</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7660818</v>
+        <v>7660828</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.94075081582385134</v>
+        <v>0.940752043826939</v>
       </c>
       <c r="AL48" s="17">
         <f>SUM(AL10:AL47)</f>
@@ -7343,15 +7343,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2359971</v>
+        <v>2359980</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>7795771</v>
+        <v>7795780</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.93792783085425646</v>
+        <v>0.93792891366575482</v>
       </c>
       <c r="AQ48" s="17">
         <f>SUM(AQ10:AQ47)</f>
@@ -7363,15 +7363,15 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2655141</v>
+        <v>2655152</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>7915050</v>
+        <v>7915061</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.93606829908535527</v>
+        <v>0.93606959999328254</v>
       </c>
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.3">

--- a/gstdatabase/GSTR-3B-2017-2018.xlsx
+++ b/gstdatabase/GSTR-3B-2017-2018.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3A4EB7-D71E-4C70-BDE9-9D7C2193E7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05970A36-801F-4225-8CE4-9CB02EDC7BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -779,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE58"/>
+  <dimension ref="A1:BE56"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="Y11" s="15">
         <f t="shared" ref="Y11:Y48" si="8">Z11-X11</f>
-        <v>21006</v>
+        <v>21007</v>
       </c>
       <c r="Z11" s="13">
-        <v>56387</v>
+        <v>56388</v>
       </c>
       <c r="AA11" s="14">
         <f t="shared" ref="AA11:AA48" si="9">Z11/W11</f>
-        <v>0.94086532846106352</v>
+        <v>0.9408820143164639</v>
       </c>
       <c r="AB11" s="12">
         <v>60956</v>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="O14" s="15">
         <f t="shared" si="4"/>
-        <v>56722</v>
+        <v>56723</v>
       </c>
       <c r="P14" s="13">
-        <v>93508</v>
+        <v>93509</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="5"/>
-        <v>0.9343512060592738</v>
+        <v>0.93436119826535302</v>
       </c>
       <c r="R14" s="12">
         <v>94880</v>
@@ -1817,14 +1817,14 @@
       </c>
       <c r="Y14" s="15">
         <f t="shared" si="8"/>
-        <v>38458</v>
+        <v>38459</v>
       </c>
       <c r="Z14" s="13">
-        <v>89002</v>
+        <v>89003</v>
       </c>
       <c r="AA14" s="14">
         <f t="shared" si="9"/>
-        <v>0.91086980994974975</v>
+        <v>0.91088004421201296</v>
       </c>
       <c r="AB14" s="12">
         <v>99756</v>
@@ -1834,14 +1834,14 @@
       </c>
       <c r="AD14" s="15">
         <f t="shared" si="10"/>
-        <v>31360</v>
+        <v>31361</v>
       </c>
       <c r="AE14" s="22">
-        <v>90287</v>
+        <v>90288</v>
       </c>
       <c r="AF14" s="14">
         <f t="shared" si="11"/>
-        <v>0.90507839127471035</v>
+        <v>0.90508841573439192</v>
       </c>
       <c r="AG14" s="12">
         <v>102558</v>
@@ -2071,14 +2071,14 @@
       </c>
       <c r="E16" s="12">
         <f t="shared" si="0"/>
-        <v>141375</v>
+        <v>141376</v>
       </c>
       <c r="F16" s="13">
-        <v>448547</v>
+        <v>448548</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="1"/>
-        <v>1.0125945892254069</v>
+        <v>1.0125968467248199</v>
       </c>
       <c r="H16" s="12">
         <v>492379</v>
@@ -2283,14 +2283,14 @@
       </c>
       <c r="T17" s="15">
         <f t="shared" si="6"/>
-        <v>153460</v>
+        <v>153462</v>
       </c>
       <c r="U17" s="13">
-        <v>405792</v>
+        <v>405794</v>
       </c>
       <c r="V17" s="14">
         <f t="shared" si="7"/>
-        <v>0.96908792174544345</v>
+        <v>0.96909269802453102</v>
       </c>
       <c r="W17" s="12">
         <v>427452</v>
@@ -2300,14 +2300,14 @@
       </c>
       <c r="Y17" s="15">
         <f t="shared" si="8"/>
-        <v>127013</v>
+        <v>127014</v>
       </c>
       <c r="Z17" s="13">
-        <v>411161</v>
+        <v>411162</v>
       </c>
       <c r="AA17" s="14">
         <f t="shared" si="9"/>
-        <v>0.96188811843201105</v>
+        <v>0.96189045787597205</v>
       </c>
       <c r="AB17" s="12">
         <v>433360</v>
@@ -2368,14 +2368,14 @@
       </c>
       <c r="AS17" s="15">
         <f t="shared" si="16"/>
-        <v>143472</v>
+        <v>143473</v>
       </c>
       <c r="AT17" s="13">
-        <v>434564</v>
+        <v>434565</v>
       </c>
       <c r="AU17" s="14">
         <f t="shared" si="17"/>
-        <v>0.95322326268016999</v>
+        <v>0.95322545619657417</v>
       </c>
     </row>
     <row r="18" spans="1:47" x14ac:dyDescent="0.3">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="T18" s="15">
         <f t="shared" si="6"/>
-        <v>282967</v>
+        <v>282969</v>
       </c>
       <c r="U18" s="13">
-        <v>769619</v>
+        <v>769621</v>
       </c>
       <c r="V18" s="14">
         <f t="shared" si="7"/>
-        <v>0.95069150723377338</v>
+        <v>0.95069397778480513</v>
       </c>
       <c r="W18" s="12">
         <v>834136</v>
@@ -2461,14 +2461,14 @@
       </c>
       <c r="Y18" s="15">
         <f t="shared" si="8"/>
-        <v>224762</v>
+        <v>224764</v>
       </c>
       <c r="Z18" s="13">
-        <v>784290</v>
+        <v>784292</v>
       </c>
       <c r="AA18" s="14">
         <f t="shared" si="9"/>
-        <v>0.94024235856023475</v>
+        <v>0.9402447562507793</v>
       </c>
       <c r="AB18" s="12">
         <v>847512</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="AD18" s="15">
         <f t="shared" si="10"/>
-        <v>171868</v>
+        <v>171869</v>
       </c>
       <c r="AE18" s="22">
-        <v>793322</v>
+        <v>793323</v>
       </c>
       <c r="AF18" s="14">
         <f t="shared" si="11"/>
-        <v>0.93605990239666226</v>
+        <v>0.9360610823209583</v>
       </c>
       <c r="AG18" s="12">
         <v>871836</v>
@@ -2495,14 +2495,14 @@
       </c>
       <c r="AI18" s="15">
         <f t="shared" si="12"/>
-        <v>189357</v>
+        <v>189358</v>
       </c>
       <c r="AJ18" s="13">
-        <v>809947</v>
+        <v>809948</v>
       </c>
       <c r="AK18" s="14">
         <f t="shared" si="13"/>
-        <v>0.92901302538550823</v>
+        <v>0.92901417239022022</v>
       </c>
       <c r="AL18" s="12">
         <v>895908</v>
@@ -2512,14 +2512,14 @@
       </c>
       <c r="AN18" s="15">
         <f t="shared" si="14"/>
-        <v>198379</v>
+        <v>198380</v>
       </c>
       <c r="AO18" s="13">
-        <v>829086</v>
+        <v>829087</v>
       </c>
       <c r="AP18" s="14">
         <f t="shared" si="15"/>
-        <v>0.92541421663831558</v>
+        <v>0.92541533282435251</v>
       </c>
       <c r="AQ18" s="12">
         <v>913159</v>
@@ -2529,14 +2529,14 @@
       </c>
       <c r="AS18" s="15">
         <f t="shared" si="16"/>
-        <v>225452</v>
+        <v>225453</v>
       </c>
       <c r="AT18" s="13">
-        <v>845572</v>
+        <v>845573</v>
       </c>
       <c r="AU18" s="14">
         <f t="shared" si="17"/>
-        <v>0.92598550745269992</v>
+        <v>0.92598660255223897</v>
       </c>
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.3">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="0"/>
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="F21" s="13">
-        <v>3767</v>
+        <v>3768</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="1"/>
-        <v>0.91810870095052399</v>
+        <v>0.91835242505483794</v>
       </c>
       <c r="H21" s="12">
         <v>5300</v>
@@ -2893,14 +2893,14 @@
       </c>
       <c r="J21" s="15">
         <f t="shared" si="2"/>
-        <v>3918</v>
+        <v>3919</v>
       </c>
       <c r="K21" s="13">
-        <v>4634</v>
+        <v>4635</v>
       </c>
       <c r="L21" s="14">
         <f t="shared" si="3"/>
-        <v>0.87433962264150944</v>
+        <v>0.87452830188679243</v>
       </c>
       <c r="M21" s="12">
         <v>6068</v>
@@ -2910,14 +2910,14 @@
       </c>
       <c r="O21" s="15">
         <f t="shared" si="4"/>
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="P21" s="13">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="Q21" s="14">
         <f t="shared" si="5"/>
-        <v>0.85810810810810811</v>
+        <v>0.85827290705339487</v>
       </c>
       <c r="R21" s="12">
         <v>6212</v>
@@ -2927,14 +2927,14 @@
       </c>
       <c r="T21" s="15">
         <f t="shared" si="6"/>
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="U21" s="13">
-        <v>5380</v>
+        <v>5381</v>
       </c>
       <c r="V21" s="14">
         <f t="shared" si="7"/>
-        <v>0.86606567933032841</v>
+        <v>0.8662266580811333</v>
       </c>
       <c r="W21" s="12">
         <v>6518</v>
@@ -2944,14 +2944,14 @@
       </c>
       <c r="Y21" s="15">
         <f t="shared" si="8"/>
-        <v>3946</v>
+        <v>3947</v>
       </c>
       <c r="Z21" s="13">
-        <v>5612</v>
+        <v>5613</v>
       </c>
       <c r="AA21" s="14">
         <f t="shared" si="9"/>
-        <v>0.86100030684258977</v>
+        <v>0.86115372813746549</v>
       </c>
       <c r="AB21" s="12">
         <v>6705</v>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="AD21" s="15">
         <f t="shared" si="10"/>
-        <v>3773</v>
+        <v>3774</v>
       </c>
       <c r="AE21" s="22">
-        <v>5795</v>
+        <v>5796</v>
       </c>
       <c r="AF21" s="14">
         <f t="shared" si="11"/>
-        <v>0.86428038777032068</v>
+        <v>0.86442953020134228</v>
       </c>
       <c r="AG21" s="12">
         <v>6982</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="AI21" s="15">
         <f t="shared" si="12"/>
-        <v>3774</v>
+        <v>3775</v>
       </c>
       <c r="AJ21" s="13">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="AK21" s="14">
         <f t="shared" si="13"/>
-        <v>0.85877971927814378</v>
+        <v>0.85892294471498143</v>
       </c>
       <c r="AL21" s="12">
         <v>7381</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="AN21" s="15">
         <f t="shared" si="14"/>
-        <v>3871</v>
+        <v>3872</v>
       </c>
       <c r="AO21" s="13">
-        <v>6277</v>
+        <v>6278</v>
       </c>
       <c r="AP21" s="14">
         <f t="shared" si="15"/>
-        <v>0.8504267714401843</v>
+        <v>0.85056225443706812</v>
       </c>
       <c r="AQ21" s="12">
         <v>8072</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="AS21" s="15">
         <f t="shared" si="16"/>
-        <v>4500</v>
+        <v>4501</v>
       </c>
       <c r="AT21" s="13">
-        <v>6792</v>
+        <v>6793</v>
       </c>
       <c r="AU21" s="14">
         <f t="shared" si="17"/>
-        <v>0.84142715559960357</v>
+        <v>0.84155104063429143</v>
       </c>
     </row>
     <row r="22" spans="1:47" x14ac:dyDescent="0.3">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="E24" s="12">
         <f t="shared" si="0"/>
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="F24" s="13">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="1"/>
-        <v>0.926968584251326</v>
+        <v>0.92778457772337819</v>
       </c>
       <c r="H24" s="12">
         <v>2976</v>
@@ -3376,14 +3376,14 @@
       </c>
       <c r="J24" s="15">
         <f t="shared" si="2"/>
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K24" s="13">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="L24" s="14">
         <f t="shared" si="3"/>
-        <v>0.8998655913978495</v>
+        <v>0.90020161290322576</v>
       </c>
       <c r="M24" s="12">
         <v>3300</v>
@@ -3393,14 +3393,14 @@
       </c>
       <c r="O24" s="15">
         <f t="shared" si="4"/>
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="P24" s="13">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="Q24" s="14">
         <f t="shared" si="5"/>
-        <v>0.88515151515151513</v>
+        <v>0.88545454545454549</v>
       </c>
       <c r="R24" s="12">
         <v>3491</v>
@@ -3410,14 +3410,14 @@
       </c>
       <c r="T24" s="15">
         <f t="shared" si="6"/>
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="U24" s="13">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="V24" s="14">
         <f t="shared" si="7"/>
-        <v>0.87510741907762823</v>
+        <v>0.87539386995130331</v>
       </c>
       <c r="W24" s="12">
         <v>3656</v>
@@ -3427,14 +3427,14 @@
       </c>
       <c r="Y24" s="15">
         <f t="shared" si="8"/>
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="Z24" s="13">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="AA24" s="14">
         <f t="shared" si="9"/>
-        <v>0.8610503282275711</v>
+        <v>0.86132385120350108</v>
       </c>
       <c r="AB24" s="12">
         <v>3748</v>
@@ -3444,14 +3444,14 @@
       </c>
       <c r="AD24" s="15">
         <f t="shared" si="10"/>
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="AE24" s="22">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="AF24" s="14">
         <f t="shared" si="11"/>
-        <v>0.85245464247598723</v>
+        <v>0.85272145144076839</v>
       </c>
       <c r="AG24" s="12">
         <v>3817</v>
@@ -3461,14 +3461,14 @@
       </c>
       <c r="AI24" s="15">
         <f t="shared" si="12"/>
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="AJ24" s="13">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="AK24" s="14">
         <f t="shared" si="13"/>
-        <v>0.84988210636625627</v>
+        <v>0.85014409221902021</v>
       </c>
       <c r="AL24" s="12">
         <v>3954</v>
@@ -3478,14 +3478,14 @@
       </c>
       <c r="AN24" s="15">
         <f t="shared" si="14"/>
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="AO24" s="13">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="AP24" s="14">
         <f t="shared" si="15"/>
-        <v>0.8434496712190187</v>
+        <v>0.8437025796661608</v>
       </c>
       <c r="AQ24" s="12">
         <v>4048</v>
@@ -3495,14 +3495,14 @@
       </c>
       <c r="AS24" s="15">
         <f t="shared" si="16"/>
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="AT24" s="13">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="AU24" s="14">
         <f t="shared" si="17"/>
-        <v>0.83621541501976282</v>
+        <v>0.83646245059288538</v>
       </c>
     </row>
     <row r="25" spans="1:47" x14ac:dyDescent="0.3">
@@ -4732,14 +4732,14 @@
       </c>
       <c r="AD32" s="15">
         <f t="shared" si="10"/>
-        <v>82134</v>
+        <v>82135</v>
       </c>
       <c r="AE32" s="22">
-        <v>268916</v>
+        <v>268917</v>
       </c>
       <c r="AF32" s="14">
         <f t="shared" si="11"/>
-        <v>0.93746971445304739</v>
+        <v>0.93747320055917138</v>
       </c>
       <c r="AG32" s="12">
         <v>294248</v>
@@ -4808,14 +4808,14 @@
       </c>
       <c r="E33" s="12">
         <f t="shared" si="0"/>
-        <v>244051</v>
+        <v>244052</v>
       </c>
       <c r="F33" s="13">
-        <v>555715</v>
+        <v>555716</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="1"/>
-        <v>0.98436954754233097</v>
+        <v>0.9843713188991372</v>
       </c>
       <c r="H33" s="12">
         <v>641658</v>
@@ -4825,14 +4825,14 @@
       </c>
       <c r="J33" s="15">
         <f t="shared" si="2"/>
-        <v>381815</v>
+        <v>381818</v>
       </c>
       <c r="K33" s="13">
-        <v>630531</v>
+        <v>630534</v>
       </c>
       <c r="L33" s="14">
         <f t="shared" si="3"/>
-        <v>0.98265898656293538</v>
+        <v>0.98266366195075883</v>
       </c>
       <c r="M33" s="12">
         <v>682019</v>
@@ -4842,14 +4842,14 @@
       </c>
       <c r="O33" s="15">
         <f t="shared" si="4"/>
-        <v>322823</v>
+        <v>322826</v>
       </c>
       <c r="P33" s="13">
-        <v>671740</v>
+        <v>671743</v>
       </c>
       <c r="Q33" s="14">
         <f t="shared" si="5"/>
-        <v>0.98492857237115095</v>
+        <v>0.98493297107558586</v>
       </c>
       <c r="R33" s="12">
         <v>673475</v>
@@ -4859,14 +4859,14 @@
       </c>
       <c r="T33" s="15">
         <f t="shared" si="6"/>
-        <v>271306</v>
+        <v>271309</v>
       </c>
       <c r="U33" s="13">
-        <v>662051</v>
+        <v>662054</v>
       </c>
       <c r="V33" s="14">
         <f t="shared" si="7"/>
-        <v>0.98303723226548867</v>
+        <v>0.98304168677382231</v>
       </c>
       <c r="W33" s="12">
         <v>688205</v>
@@ -4876,14 +4876,14 @@
       </c>
       <c r="Y33" s="15">
         <f t="shared" si="8"/>
-        <v>206624</v>
+        <v>206626</v>
       </c>
       <c r="Z33" s="13">
-        <v>674448</v>
+        <v>674450</v>
       </c>
       <c r="AA33" s="14">
         <f t="shared" si="9"/>
-        <v>0.98001031669342709</v>
+        <v>0.98001322280425163</v>
       </c>
       <c r="AB33" s="12">
         <v>698869</v>
@@ -4893,14 +4893,14 @@
       </c>
       <c r="AD33" s="15">
         <f t="shared" si="10"/>
-        <v>160028</v>
+        <v>160029</v>
       </c>
       <c r="AE33" s="22">
-        <v>684448</v>
+        <v>684449</v>
       </c>
       <c r="AF33" s="14">
         <f t="shared" si="11"/>
-        <v>0.97936523153838562</v>
+        <v>0.97936666242171277</v>
       </c>
       <c r="AG33" s="12">
         <v>712579</v>
@@ -4910,14 +4910,14 @@
       </c>
       <c r="AI33" s="15">
         <f t="shared" si="12"/>
-        <v>175971</v>
+        <v>175973</v>
       </c>
       <c r="AJ33" s="13">
-        <v>696870</v>
+        <v>696872</v>
       </c>
       <c r="AK33" s="14">
         <f t="shared" si="13"/>
-        <v>0.97795472501996272</v>
+        <v>0.97795753172630684</v>
       </c>
       <c r="AL33" s="12">
         <v>723682</v>
@@ -4927,14 +4927,14 @@
       </c>
       <c r="AN33" s="15">
         <f t="shared" si="14"/>
-        <v>176020</v>
+        <v>176022</v>
       </c>
       <c r="AO33" s="13">
-        <v>707224</v>
+        <v>707226</v>
       </c>
       <c r="AP33" s="14">
         <f t="shared" si="15"/>
-        <v>0.97725796689706257</v>
+        <v>0.97726073054186779</v>
       </c>
       <c r="AQ33" s="12">
         <v>733311</v>
@@ -4944,14 +4944,14 @@
       </c>
       <c r="AS33" s="15">
         <f t="shared" si="16"/>
-        <v>199520</v>
+        <v>199523</v>
       </c>
       <c r="AT33" s="13">
-        <v>716004</v>
+        <v>716007</v>
       </c>
       <c r="AU33" s="14">
         <f t="shared" si="17"/>
-        <v>0.9763988266915401</v>
+        <v>0.97640291772522159</v>
       </c>
     </row>
     <row r="34" spans="1:47" x14ac:dyDescent="0.3">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="O36" s="15">
         <f t="shared" si="4"/>
-        <v>484934</v>
+        <v>484936</v>
       </c>
       <c r="P36" s="13">
-        <v>1042171</v>
+        <v>1042173</v>
       </c>
       <c r="Q36" s="14">
         <f t="shared" si="5"/>
-        <v>0.982698110360955</v>
+        <v>0.98269999622826543</v>
       </c>
       <c r="R36" s="12">
         <v>1054857</v>
@@ -5342,14 +5342,14 @@
       </c>
       <c r="T36" s="15">
         <f t="shared" si="6"/>
-        <v>445769</v>
+        <v>445770</v>
       </c>
       <c r="U36" s="13">
-        <v>1031367</v>
+        <v>1031368</v>
       </c>
       <c r="V36" s="14">
         <f t="shared" si="7"/>
-        <v>0.97773157878271655</v>
+        <v>0.97773252677851119</v>
       </c>
       <c r="W36" s="12">
         <v>1076657</v>
@@ -5393,14 +5393,14 @@
       </c>
       <c r="AI36" s="15">
         <f t="shared" si="12"/>
-        <v>353172</v>
+        <v>353173</v>
       </c>
       <c r="AJ36" s="13">
-        <v>1078134</v>
+        <v>1078135</v>
       </c>
       <c r="AK36" s="14">
         <f t="shared" si="13"/>
-        <v>0.96774697369814711</v>
+        <v>0.96774787131103546</v>
       </c>
       <c r="AL36" s="12">
         <v>1133258</v>
@@ -5452,14 +5452,14 @@
       </c>
       <c r="E37" s="12">
         <f t="shared" si="0"/>
-        <v>234916</v>
+        <v>234917</v>
       </c>
       <c r="F37" s="13">
-        <v>499886</v>
+        <v>499887</v>
       </c>
       <c r="G37" s="14">
         <f t="shared" si="1"/>
-        <v>0.99300565943659902</v>
+        <v>0.99300764590083168</v>
       </c>
       <c r="H37" s="12">
         <v>530355</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="J37" s="15">
         <f t="shared" si="2"/>
-        <v>309554</v>
+        <v>309555</v>
       </c>
       <c r="K37" s="13">
-        <v>519226</v>
+        <v>519227</v>
       </c>
       <c r="L37" s="14">
         <f t="shared" si="3"/>
-        <v>0.97901594215195487</v>
+        <v>0.97901782768145862</v>
       </c>
       <c r="M37" s="12">
         <v>553919</v>
@@ -5486,14 +5486,14 @@
       </c>
       <c r="O37" s="15">
         <f t="shared" si="4"/>
-        <v>252342</v>
+        <v>252343</v>
       </c>
       <c r="P37" s="13">
-        <v>538158</v>
+        <v>538159</v>
       </c>
       <c r="Q37" s="14">
         <f t="shared" si="5"/>
-        <v>0.97154638133012228</v>
+        <v>0.9715481866482284</v>
       </c>
       <c r="R37" s="12">
         <v>537199</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="T37" s="15">
         <f t="shared" si="6"/>
-        <v>196451</v>
+        <v>196453</v>
       </c>
       <c r="U37" s="13">
-        <v>514131</v>
+        <v>514133</v>
       </c>
       <c r="V37" s="14">
         <f t="shared" si="7"/>
-        <v>0.95705874359408716</v>
+        <v>0.95706246660920813</v>
       </c>
       <c r="W37" s="12">
         <v>549345</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="Y37" s="15">
         <f t="shared" si="8"/>
-        <v>170962</v>
+        <v>170963</v>
       </c>
       <c r="Z37" s="13">
-        <v>518614</v>
+        <v>518615</v>
       </c>
       <c r="AA37" s="14">
         <f t="shared" si="9"/>
-        <v>0.94405883370195409</v>
+        <v>0.9440606540516433</v>
       </c>
       <c r="AB37" s="12">
         <v>556414</v>
@@ -5554,14 +5554,14 @@
       </c>
       <c r="AI37" s="15">
         <f t="shared" si="12"/>
-        <v>151242</v>
+        <v>151243</v>
       </c>
       <c r="AJ37" s="13">
-        <v>531704</v>
+        <v>531705</v>
       </c>
       <c r="AK37" s="14">
         <f t="shared" si="13"/>
-        <v>0.93578556468786844</v>
+        <v>0.9357873246625249</v>
       </c>
       <c r="AL37" s="12">
         <v>579378</v>
@@ -5571,14 +5571,14 @@
       </c>
       <c r="AN37" s="15">
         <f t="shared" si="14"/>
-        <v>159383</v>
+        <v>159384</v>
       </c>
       <c r="AO37" s="13">
-        <v>539982</v>
+        <v>539983</v>
       </c>
       <c r="AP37" s="14">
         <f t="shared" si="15"/>
-        <v>0.93200294108509474</v>
+        <v>0.93200466707400009</v>
       </c>
       <c r="AQ37" s="12">
         <v>590015</v>
@@ -5588,14 +5588,14 @@
       </c>
       <c r="AS37" s="15">
         <f t="shared" si="16"/>
-        <v>175710</v>
+        <v>175711</v>
       </c>
       <c r="AT37" s="13">
-        <v>547813</v>
+        <v>547814</v>
       </c>
       <c r="AU37" s="14">
         <f t="shared" si="17"/>
-        <v>0.92847300492360363</v>
+        <v>0.92847469979576791</v>
       </c>
     </row>
     <row r="38" spans="1:47" x14ac:dyDescent="0.3">
@@ -6003,14 +6003,14 @@
       </c>
       <c r="Y40" s="15">
         <f t="shared" si="8"/>
-        <v>87870</v>
+        <v>87871</v>
       </c>
       <c r="Z40" s="13">
-        <v>226908</v>
+        <v>226909</v>
       </c>
       <c r="AA40" s="14">
         <f t="shared" si="9"/>
-        <v>0.97558752461455123</v>
+        <v>0.97559182409947287</v>
       </c>
       <c r="AB40" s="12">
         <v>234754</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="E41" s="12">
         <f t="shared" si="0"/>
-        <v>291301</v>
+        <v>291304</v>
       </c>
       <c r="F41" s="13">
-        <v>603818</v>
+        <v>603821</v>
       </c>
       <c r="G41" s="14">
         <f t="shared" si="1"/>
-        <v>0.96631597814571446</v>
+        <v>0.9663207791750551</v>
       </c>
       <c r="H41" s="12">
         <v>673862</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="J41" s="15">
         <f t="shared" si="2"/>
-        <v>440804</v>
+        <v>440806</v>
       </c>
       <c r="K41" s="13">
-        <v>643248</v>
+        <v>643250</v>
       </c>
       <c r="L41" s="14">
         <f t="shared" si="3"/>
-        <v>0.95456933318691362</v>
+        <v>0.95457230115364866</v>
       </c>
       <c r="M41" s="12">
         <v>700632</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="O41" s="15">
         <f t="shared" si="4"/>
-        <v>341596</v>
+        <v>341601</v>
       </c>
       <c r="P41" s="13">
-        <v>665628</v>
+        <v>665633</v>
       </c>
       <c r="Q41" s="14">
         <f t="shared" si="5"/>
-        <v>0.95003939300517248</v>
+        <v>0.95004652941915302</v>
       </c>
       <c r="R41" s="12">
         <v>688720</v>
@@ -6147,14 +6147,14 @@
       </c>
       <c r="T41" s="15">
         <f t="shared" si="6"/>
-        <v>252613</v>
+        <v>252618</v>
       </c>
       <c r="U41" s="13">
-        <v>648486</v>
+        <v>648491</v>
       </c>
       <c r="V41" s="14">
         <f t="shared" si="7"/>
-        <v>0.94158148449297252</v>
+        <v>0.94158874433732143</v>
       </c>
       <c r="W41" s="12">
         <v>702649</v>
@@ -6164,14 +6164,14 @@
       </c>
       <c r="Y41" s="15">
         <f t="shared" si="8"/>
-        <v>224611</v>
+        <v>224614</v>
       </c>
       <c r="Z41" s="13">
-        <v>653176</v>
+        <v>653179</v>
       </c>
       <c r="AA41" s="14">
         <f t="shared" si="9"/>
-        <v>0.92959073449190133</v>
+        <v>0.92959500404896334</v>
       </c>
       <c r="AB41" s="12">
         <v>712131</v>
@@ -6181,14 +6181,14 @@
       </c>
       <c r="AD41" s="15">
         <f t="shared" si="10"/>
-        <v>204659</v>
+        <v>204664</v>
       </c>
       <c r="AE41" s="22">
-        <v>658371</v>
+        <v>658376</v>
       </c>
       <c r="AF41" s="14">
         <f t="shared" si="11"/>
-        <v>0.92450827165226623</v>
+        <v>0.92451529283235812</v>
       </c>
       <c r="AG41" s="12">
         <v>722496</v>
@@ -6198,14 +6198,14 @@
       </c>
       <c r="AI41" s="15">
         <f t="shared" si="12"/>
-        <v>206306</v>
+        <v>206310</v>
       </c>
       <c r="AJ41" s="13">
-        <v>665050</v>
+        <v>665054</v>
       </c>
       <c r="AK41" s="14">
         <f t="shared" si="13"/>
-        <v>0.92048952520152361</v>
+        <v>0.92049506156435468</v>
       </c>
       <c r="AL41" s="12">
         <v>737038</v>
@@ -6215,14 +6215,14 @@
       </c>
       <c r="AN41" s="15">
         <f t="shared" si="14"/>
-        <v>213610</v>
+        <v>213614</v>
       </c>
       <c r="AO41" s="13">
-        <v>675125</v>
+        <v>675129</v>
       </c>
       <c r="AP41" s="14">
         <f t="shared" si="15"/>
-        <v>0.91599754693787838</v>
+        <v>0.91600297406646602</v>
       </c>
       <c r="AQ41" s="12">
         <v>750910</v>
@@ -6232,14 +6232,14 @@
       </c>
       <c r="AS41" s="15">
         <f t="shared" si="16"/>
-        <v>230887</v>
+        <v>230893</v>
       </c>
       <c r="AT41" s="13">
-        <v>684744</v>
+        <v>684750</v>
       </c>
       <c r="AU41" s="14">
         <f t="shared" si="17"/>
-        <v>0.9118855788310184</v>
+        <v>0.91189356913611486</v>
       </c>
     </row>
     <row r="42" spans="1:47" x14ac:dyDescent="0.3">
@@ -6613,14 +6613,14 @@
       </c>
       <c r="O44" s="15">
         <f t="shared" si="4"/>
-        <v>131885</v>
+        <v>131886</v>
       </c>
       <c r="P44" s="13">
-        <v>222520</v>
+        <v>222521</v>
       </c>
       <c r="Q44" s="14">
         <f t="shared" si="5"/>
-        <v>0.94731688626833266</v>
+        <v>0.94732114348964436</v>
       </c>
       <c r="R44" s="12">
         <v>230496</v>
@@ -7203,15 +7203,15 @@
       </c>
       <c r="E48" s="18">
         <f t="shared" si="0"/>
-        <v>2850826</v>
+        <v>2850835</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>6617089</v>
+        <v>6617098</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" ref="G48" si="18">F48/C48</f>
-        <v>0.97545547054811255</v>
+        <v>0.97545679727943424</v>
       </c>
       <c r="H48" s="17">
         <f>SUM(H10:H47)</f>
@@ -7223,15 +7223,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>4422329</v>
+        <v>4422337</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>7216088</v>
+        <v>7216096</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.96507348565152762</v>
+        <v>0.96507455556473898</v>
       </c>
       <c r="M48" s="17">
         <f>SUM(M10:M47)</f>
@@ -7243,15 +7243,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>3706427</v>
+        <v>3706442</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>7574210</v>
+        <v>7574225</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.96646347337648142</v>
+        <v>0.96646538736514831</v>
       </c>
       <c r="R48" s="17">
         <f>SUM(R10:R47)</f>
@@ -7263,15 +7263,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>2999213</v>
+        <v>2999230</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>7326937</v>
+        <v>7326954</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.95806121889919171</v>
+        <v>0.95806344179816316</v>
       </c>
       <c r="W48" s="17">
         <f>SUM(W10:W47)</f>
@@ -7283,15 +7283,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2552763</v>
+        <v>2552777</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>7437199</v>
+        <v>7437213</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.9483404804439497</v>
+        <v>0.94834226562768975</v>
       </c>
       <c r="AB48" s="17">
         <f>SUM(AB10:AB47)</f>
@@ -7303,15 +7303,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>2124161</v>
+        <v>2124172</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>7529910</v>
+        <v>7529921</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.94467784971187607</v>
+        <v>0.94467922973585339</v>
       </c>
       <c r="AG48" s="17">
         <f>SUM(AG10:AG47)</f>
@@ -7323,15 +7323,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2280254</v>
+        <v>2280265</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7660828</v>
+        <v>7660839</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.940752043826939</v>
+        <v>0.94075339463033547</v>
       </c>
       <c r="AL48" s="17">
         <f>SUM(AL10:AL47)</f>
@@ -7343,15 +7343,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2359980</v>
+        <v>2359990</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>7795780</v>
+        <v>7795790</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.93792891366575482</v>
+        <v>0.937930116789642</v>
       </c>
       <c r="AQ48" s="17">
         <f>SUM(AQ10:AQ47)</f>
@@ -7363,32 +7363,32 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2655152</v>
+        <v>2655166</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>7915061</v>
+        <v>7915075</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.93606959999328254</v>
+        <v>0.93607125569428096</v>
       </c>
     </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
+    <row r="55" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="A55" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="4"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="4"/>
     </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="AV58">
+    <row r="56" spans="1:49" x14ac:dyDescent="0.3">
+      <c r="AV56">
         <v>24985627</v>
       </c>
-      <c r="AW58">
+      <c r="AW56">
         <v>66107624</v>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="W8:AA8"/>
